--- a/Backtest/strategy_playbook.xlsx
+++ b/Backtest/strategy_playbook.xlsx
@@ -484,7 +484,7 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
   </cols>
@@ -532,7 +532,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Losses Harvested</t>
+          <t>Realized Losses (All)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -1564,7 +1564,7 @@
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>Losses Harvested</t>
+          <t>Realized Losses (All)</t>
         </is>
       </c>
       <c r="K1" s="4" t="inlineStr">
@@ -7024,7 +7024,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>Losses Harvested</t>
+          <t>Realized Losses (All)</t>
         </is>
       </c>
       <c r="K1" s="5" t="inlineStr">
@@ -12178,7 +12178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC193"/>
+  <dimension ref="A1:AE193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -12199,17 +12199,19 @@
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="17" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="20" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
-    <col width="23" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="22" max="22"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
+    <col width="23" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12305,55 +12307,65 @@
       </c>
       <c r="S1" s="6" t="inlineStr">
         <is>
-          <t>Losses Harvested</t>
+          <t>Realized Losses (All)</t>
         </is>
       </c>
       <c r="T1" s="6" t="inlineStr">
         <is>
+          <t>TLH Losses</t>
+        </is>
+      </c>
+      <c r="U1" s="6" t="inlineStr">
+        <is>
+          <t>Rebal Losses</t>
+        </is>
+      </c>
+      <c r="V1" s="6" t="inlineStr">
+        <is>
           <t>TLH Event Count</t>
         </is>
       </c>
-      <c r="U1" s="6" t="inlineStr">
+      <c r="W1" s="6" t="inlineStr">
         <is>
           <t>Execution Costs</t>
         </is>
       </c>
-      <c r="V1" s="6" t="inlineStr">
+      <c r="X1" s="6" t="inlineStr">
         <is>
           <t>Tax Alpha 2</t>
         </is>
       </c>
-      <c r="W1" s="6" t="inlineStr">
+      <c r="Y1" s="6" t="inlineStr">
         <is>
           <t>Loss Carryforward ST</t>
         </is>
       </c>
-      <c r="X1" s="6" t="inlineStr">
+      <c r="Z1" s="6" t="inlineStr">
         <is>
           <t>Loss Carryforward LT</t>
         </is>
       </c>
-      <c r="Y1" s="6" t="inlineStr">
+      <c r="AA1" s="6" t="inlineStr">
         <is>
           <t>Liquidation NAV</t>
         </is>
       </c>
-      <c r="Z1" s="6" t="inlineStr">
+      <c r="AB1" s="6" t="inlineStr">
         <is>
           <t>Unrealized Gain ST</t>
         </is>
       </c>
-      <c r="AA1" s="6" t="inlineStr">
+      <c r="AC1" s="6" t="inlineStr">
         <is>
           <t>Unrealized Gain LT</t>
         </is>
       </c>
-      <c r="AB1" s="6" t="inlineStr">
+      <c r="AD1" s="6" t="inlineStr">
         <is>
           <t>Liquidation Tax</t>
         </is>
       </c>
-      <c r="AC1" s="6" t="inlineStr">
+      <c r="AE1" s="6" t="inlineStr">
         <is>
           <t>Liquidation Exec Cost</t>
         </is>
@@ -12433,28 +12445,34 @@
         <v>0</v>
       </c>
       <c r="U2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="2" t="n">
         <v>621291.05</v>
       </c>
-      <c r="Z2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="2" t="n">
+      <c r="AB2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="2" t="n">
         <v>-377815.2</v>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AD2" s="2" t="n">
         <v>-1050</v>
       </c>
-      <c r="AC2" s="2" t="n">
+      <c r="AE2" s="2" t="n">
         <v>745.1799999999999</v>
       </c>
     </row>
@@ -12529,33 +12547,39 @@
         <v>360305.74</v>
       </c>
       <c r="T3" s="3" t="n">
+        <v>360305.7379450751</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="W3" s="3" t="n">
         <v>6249.97</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" s="3" t="n">
         <v>-2362.366846883669</v>
       </c>
-      <c r="W3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="3" t="n">
         <v>618931.52</v>
       </c>
-      <c r="Z3" s="3" t="n">
+      <c r="AB3" s="3" t="n">
         <v>42315.74</v>
       </c>
-      <c r="AA3" s="3" t="n">
+      <c r="AC3" s="3" t="n">
         <v>-57136.16</v>
       </c>
-      <c r="AB3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="3" t="n">
+      <c r="AD3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
         <v>742.35</v>
       </c>
     </row>
@@ -12633,28 +12657,34 @@
         <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X4" s="2" t="inlineStr"/>
       <c r="Y4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="2" t="n">
         <v>621291.05</v>
       </c>
-      <c r="Z4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AB4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="2" t="n">
         <v>-377815.2</v>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AD4" s="2" t="n">
         <v>-1050</v>
       </c>
-      <c r="AC4" s="2" t="n">
+      <c r="AE4" s="2" t="n">
         <v>745.1799999999999</v>
       </c>
     </row>
@@ -12729,33 +12759,39 @@
         <v>360305.74</v>
       </c>
       <c r="T5" s="3" t="n">
+        <v>360305.7379450751</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="U5" s="3" t="n">
+      <c r="W5" s="3" t="n">
         <v>6249.97</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" s="3" t="n">
         <v>-2362.366846883669</v>
       </c>
-      <c r="W5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="3" t="n">
         <v>618931.52</v>
       </c>
-      <c r="Z5" s="3" t="n">
+      <c r="AB5" s="3" t="n">
         <v>42315.74</v>
       </c>
-      <c r="AA5" s="3" t="n">
+      <c r="AC5" s="3" t="n">
         <v>-57136.16</v>
       </c>
-      <c r="AB5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="3" t="n">
+      <c r="AD5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
         <v>742.35</v>
       </c>
     </row>
@@ -12833,28 +12869,34 @@
         <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X6" s="2" t="inlineStr"/>
       <c r="Y6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="2" t="n">
         <v>621291.05</v>
       </c>
-      <c r="Z6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="2" t="n">
+      <c r="AB6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2" t="n">
         <v>-377815.2</v>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AD6" s="2" t="n">
         <v>-1050</v>
       </c>
-      <c r="AC6" s="2" t="n">
+      <c r="AE6" s="2" t="n">
         <v>745.1799999999999</v>
       </c>
     </row>
@@ -12929,33 +12971,39 @@
         <v>360305.74</v>
       </c>
       <c r="T7" s="3" t="n">
+        <v>360305.7379450751</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="W7" s="3" t="n">
         <v>6249.97</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" s="3" t="n">
         <v>-2362.366846883669</v>
       </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3" t="n">
         <v>618931.52</v>
       </c>
-      <c r="Z7" s="3" t="n">
+      <c r="AB7" s="3" t="n">
         <v>42315.74</v>
       </c>
-      <c r="AA7" s="3" t="n">
+      <c r="AC7" s="3" t="n">
         <v>-57136.16</v>
       </c>
-      <c r="AB7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="3" t="n">
+      <c r="AD7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
         <v>742.35</v>
       </c>
     </row>
@@ -13035,28 +13083,34 @@
         <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
+        <v>11371.78997278146</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
         <v>1498.47</v>
       </c>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X8" s="2" t="inlineStr"/>
       <c r="Y8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="2" t="n">
         <v>621384</v>
       </c>
-      <c r="Z8" s="2" t="n">
+      <c r="AB8" s="2" t="n">
         <v>-11915.19</v>
       </c>
-      <c r="AA8" s="2" t="n">
+      <c r="AC8" s="2" t="n">
         <v>-358362.18</v>
       </c>
-      <c r="AB8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="2" t="n">
+      <c r="AD8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="2" t="n">
         <v>745.3</v>
       </c>
     </row>
@@ -13133,33 +13187,39 @@
         <v>279032.99</v>
       </c>
       <c r="T9" s="3" t="n">
+        <v>249286.2037586212</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>29746.78717139569</v>
+      </c>
+      <c r="V9" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="U9" s="3" t="n">
+      <c r="W9" s="3" t="n">
         <v>7203.88</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="X9" s="3" t="n">
         <v>25106.9648084396</v>
       </c>
-      <c r="W9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="3" t="n">
         <v>646460.83</v>
       </c>
-      <c r="Z9" s="3" t="n">
+      <c r="AB9" s="3" t="n">
         <v>-21127.37</v>
       </c>
-      <c r="AA9" s="3" t="n">
+      <c r="AC9" s="3" t="n">
         <v>-57034.11</v>
       </c>
-      <c r="AB9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="3" t="n">
+      <c r="AD9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
         <v>775.42</v>
       </c>
     </row>
@@ -13239,28 +13299,34 @@
         <v>0</v>
       </c>
       <c r="U10" s="2" t="n">
+        <v>4323.455209702924</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="2" t="n">
         <v>1349.81</v>
       </c>
-      <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X10" s="2" t="inlineStr"/>
       <c r="Y10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2" t="n">
         <v>621423.62</v>
       </c>
-      <c r="Z10" s="2" t="n">
+      <c r="AB10" s="2" t="n">
         <v>-9117.280000000001</v>
       </c>
-      <c r="AA10" s="2" t="n">
+      <c r="AC10" s="2" t="n">
         <v>-367371.2</v>
       </c>
-      <c r="AB10" s="2" t="n">
+      <c r="AD10" s="2" t="n">
         <v>-854.34</v>
       </c>
-      <c r="AC10" s="2" t="n">
+      <c r="AE10" s="2" t="n">
         <v>745.34</v>
       </c>
     </row>
@@ -13337,33 +13403,39 @@
         <v>378268.7</v>
       </c>
       <c r="T11" s="3" t="n">
+        <v>338212.6580272673</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>40056.04286945938</v>
+      </c>
+      <c r="V11" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="U11" s="3" t="n">
+      <c r="W11" s="3" t="n">
         <v>9680.58</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="X11" s="3" t="n">
         <v>-7485.61122415401</v>
       </c>
-      <c r="W11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="3" t="n">
         <v>613946.99</v>
       </c>
-      <c r="Z11" s="3" t="n">
+      <c r="AB11" s="3" t="n">
         <v>19111.01</v>
       </c>
-      <c r="AA11" s="3" t="n">
+      <c r="AC11" s="3" t="n">
         <v>-59170.79</v>
       </c>
-      <c r="AB11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="3" t="n">
+      <c r="AD11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="3" t="n">
         <v>736.36</v>
       </c>
     </row>
@@ -13443,28 +13515,34 @@
         <v>0</v>
       </c>
       <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="2" t="n">
         <v>1263.1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr"/>
-      <c r="W12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="2" t="n">
         <v>622831.1</v>
       </c>
-      <c r="Z12" s="2" t="n">
+      <c r="AB12" s="2" t="n">
         <v>-10795.43</v>
       </c>
-      <c r="AA12" s="2" t="n">
+      <c r="AC12" s="2" t="n">
         <v>-369846.5</v>
       </c>
-      <c r="AB12" s="2" t="n">
+      <c r="AD12" s="2" t="n">
         <v>-2601.61</v>
       </c>
-      <c r="AC12" s="2" t="n">
+      <c r="AE12" s="2" t="n">
         <v>747.03</v>
       </c>
     </row>
@@ -13541,33 +13619,39 @@
         <v>336231.94</v>
       </c>
       <c r="T13" s="3" t="n">
+        <v>336231.9415210387</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="U13" s="3" t="n">
+      <c r="W13" s="3" t="n">
         <v>6226.92</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="X13" s="3" t="n">
         <v>2093.643987607327</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3" t="n">
         <v>624922.23</v>
       </c>
-      <c r="Z13" s="3" t="n">
+      <c r="AB13" s="3" t="n">
         <v>19783.64</v>
       </c>
-      <c r="AA13" s="3" t="n">
+      <c r="AC13" s="3" t="n">
         <v>-57136.16</v>
       </c>
-      <c r="AB13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="3" t="n">
+      <c r="AD13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3" t="n">
         <v>749.55</v>
       </c>
     </row>
@@ -13645,28 +13729,34 @@
         <v>0</v>
       </c>
       <c r="U14" s="2" t="n">
+        <v>8360.563627566771</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2" t="n">
         <v>1339.45</v>
       </c>
-      <c r="V14" s="2" t="inlineStr"/>
-      <c r="W14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X14" s="2" t="inlineStr"/>
       <c r="Y14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="2" t="n">
         <v>625214.78</v>
       </c>
-      <c r="Z14" s="2" t="n">
+      <c r="AB14" s="2" t="n">
         <v>-8345.58</v>
       </c>
-      <c r="AA14" s="2" t="n">
+      <c r="AC14" s="2" t="n">
         <v>-363471.48</v>
       </c>
-      <c r="AB14" s="2" t="n">
+      <c r="AD14" s="2" t="n">
         <v>-374.92</v>
       </c>
-      <c r="AC14" s="2" t="n">
+      <c r="AE14" s="2" t="n">
         <v>749.9</v>
       </c>
     </row>
@@ -13741,33 +13831,39 @@
         <v>339189.4</v>
       </c>
       <c r="T15" s="3" t="n">
+        <v>274057.0433339779</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>65132.36092576115</v>
+      </c>
+      <c r="V15" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="W15" s="3" t="n">
         <v>7519.93</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="X15" s="3" t="n">
         <v>7553.037601362914</v>
       </c>
-      <c r="W15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3" t="n">
         <v>632758.76</v>
       </c>
-      <c r="Z15" s="3" t="n">
+      <c r="AB15" s="3" t="n">
         <v>-2881.11</v>
       </c>
-      <c r="AA15" s="3" t="n">
+      <c r="AC15" s="3" t="n">
         <v>-57136.16</v>
       </c>
-      <c r="AB15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="3" t="n">
+      <c r="AD15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3" t="n">
         <v>758.96</v>
       </c>
     </row>
@@ -13845,28 +13941,34 @@
         <v>0</v>
       </c>
       <c r="U16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V16" s="2" t="inlineStr"/>
-      <c r="W16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X16" s="2" t="inlineStr"/>
       <c r="Y16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="2" t="n">
         <v>621291.05</v>
       </c>
-      <c r="Z16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="2" t="n">
+      <c r="AB16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="2" t="n">
         <v>-377815.2</v>
       </c>
-      <c r="AB16" s="2" t="n">
+      <c r="AD16" s="2" t="n">
         <v>-1050</v>
       </c>
-      <c r="AC16" s="2" t="n">
+      <c r="AE16" s="2" t="n">
         <v>745.1799999999999</v>
       </c>
     </row>
@@ -13941,33 +14043,39 @@
         <v>360305.74</v>
       </c>
       <c r="T17" s="3" t="n">
+        <v>360305.7379450751</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="U17" s="3" t="n">
+      <c r="W17" s="3" t="n">
         <v>6249.97</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="X17" s="3" t="n">
         <v>-2362.366846883669</v>
       </c>
-      <c r="W17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="3" t="n">
         <v>618931.52</v>
       </c>
-      <c r="Z17" s="3" t="n">
+      <c r="AB17" s="3" t="n">
         <v>42315.74</v>
       </c>
-      <c r="AA17" s="3" t="n">
+      <c r="AC17" s="3" t="n">
         <v>-57136.16</v>
       </c>
-      <c r="AB17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="3" t="n">
+      <c r="AD17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="3" t="n">
         <v>742.35</v>
       </c>
     </row>
@@ -14045,28 +14153,34 @@
         <v>0</v>
       </c>
       <c r="U18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V18" s="2" t="inlineStr"/>
-      <c r="W18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X18" s="2" t="inlineStr"/>
       <c r="Y18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="2" t="n">
         <v>1147221.49</v>
       </c>
-      <c r="Z18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="2" t="n">
+      <c r="AB18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="2" t="n">
         <v>187304.23</v>
       </c>
-      <c r="AB18" s="2" t="n">
+      <c r="AD18" s="2" t="n">
         <v>37460.85</v>
       </c>
-      <c r="AC18" s="2" t="n">
+      <c r="AE18" s="2" t="n">
         <v>1423.33</v>
       </c>
     </row>
@@ -14141,33 +14255,39 @@
         <v>48396.51</v>
       </c>
       <c r="T19" s="3" t="n">
+        <v>48396.50725438184</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="U19" s="3" t="n">
+      <c r="W19" s="3" t="n">
         <v>2178.53</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="X19" s="3" t="n">
         <v>-9524.092741572997</v>
       </c>
-      <c r="W19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="3" t="n">
         <v>1138578.91</v>
       </c>
-      <c r="Z19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="3" t="n">
+      <c r="AB19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="3" t="n">
         <v>226106.6</v>
       </c>
-      <c r="AB19" s="3" t="n">
+      <c r="AD19" s="3" t="n">
         <v>36592.02</v>
       </c>
-      <c r="AC19" s="3" t="n">
+      <c r="AE19" s="3" t="n">
         <v>1410.64</v>
       </c>
     </row>
@@ -14245,28 +14365,34 @@
         <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V20" s="2" t="inlineStr"/>
-      <c r="W20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X20" s="2" t="inlineStr"/>
       <c r="Y20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="2" t="n">
         <v>1147221.49</v>
       </c>
-      <c r="Z20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="2" t="n">
+      <c r="AB20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="2" t="n">
         <v>187304.23</v>
       </c>
-      <c r="AB20" s="2" t="n">
+      <c r="AD20" s="2" t="n">
         <v>37460.85</v>
       </c>
-      <c r="AC20" s="2" t="n">
+      <c r="AE20" s="2" t="n">
         <v>1423.33</v>
       </c>
     </row>
@@ -14341,33 +14467,39 @@
         <v>48396.51</v>
       </c>
       <c r="T21" s="3" t="n">
+        <v>48396.50725438184</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="U21" s="3" t="n">
+      <c r="W21" s="3" t="n">
         <v>2178.53</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="X21" s="3" t="n">
         <v>-9524.092741572997</v>
       </c>
-      <c r="W21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3" t="n">
         <v>1138578.91</v>
       </c>
-      <c r="Z21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="3" t="n">
+      <c r="AB21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3" t="n">
         <v>226106.6</v>
       </c>
-      <c r="AB21" s="3" t="n">
+      <c r="AD21" s="3" t="n">
         <v>36592.02</v>
       </c>
-      <c r="AC21" s="3" t="n">
+      <c r="AE21" s="3" t="n">
         <v>1410.64</v>
       </c>
     </row>
@@ -14445,28 +14577,34 @@
         <v>0</v>
       </c>
       <c r="U22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V22" s="2" t="inlineStr"/>
-      <c r="W22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X22" s="2" t="inlineStr"/>
       <c r="Y22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2" t="n">
         <v>1147221.49</v>
       </c>
-      <c r="Z22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="2" t="n">
+      <c r="AB22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="2" t="n">
         <v>187304.23</v>
       </c>
-      <c r="AB22" s="2" t="n">
+      <c r="AD22" s="2" t="n">
         <v>37460.85</v>
       </c>
-      <c r="AC22" s="2" t="n">
+      <c r="AE22" s="2" t="n">
         <v>1423.33</v>
       </c>
     </row>
@@ -14541,33 +14679,39 @@
         <v>48396.51</v>
       </c>
       <c r="T23" s="3" t="n">
+        <v>48396.50725438184</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="U23" s="3" t="n">
+      <c r="W23" s="3" t="n">
         <v>2178.53</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="X23" s="3" t="n">
         <v>-9524.092741572997</v>
       </c>
-      <c r="W23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3" t="n">
         <v>1138578.91</v>
       </c>
-      <c r="Z23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="3" t="n">
+      <c r="AB23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3" t="n">
         <v>226106.6</v>
       </c>
-      <c r="AB23" s="3" t="n">
+      <c r="AD23" s="3" t="n">
         <v>36592.02</v>
       </c>
-      <c r="AC23" s="3" t="n">
+      <c r="AE23" s="3" t="n">
         <v>1410.64</v>
       </c>
     </row>
@@ -14647,28 +14791,34 @@
         <v>0</v>
       </c>
       <c r="U24" s="2" t="n">
+        <v>2518.433067748997</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="2" t="n">
         <v>1516.81</v>
       </c>
-      <c r="V24" s="2" t="inlineStr"/>
-      <c r="W24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X24" s="2" t="inlineStr"/>
       <c r="Y24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="2" t="n">
         <v>1140487.84</v>
       </c>
-      <c r="Z24" s="2" t="n">
+      <c r="AB24" s="2" t="n">
         <v>5717.55</v>
       </c>
-      <c r="AA24" s="2" t="n">
+      <c r="AC24" s="2" t="n">
         <v>168118.64</v>
       </c>
-      <c r="AB24" s="2" t="n">
+      <c r="AD24" s="2" t="n">
         <v>35548</v>
       </c>
-      <c r="AC24" s="2" t="n">
+      <c r="AE24" s="2" t="n">
         <v>1414.13</v>
       </c>
     </row>
@@ -14745,33 +14895,39 @@
         <v>54712.58</v>
       </c>
       <c r="T25" s="3" t="n">
+        <v>53672.55329355953</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>1040.022357235378</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="U25" s="3" t="n">
+      <c r="W25" s="3" t="n">
         <v>2572.08</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="X25" s="3" t="n">
         <v>-7512.47243928886</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="Y25" s="3" t="n">
         <v>28680.95943831675</v>
       </c>
-      <c r="X25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3" t="n">
+      <c r="Z25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3" t="n">
         <v>1132384.96</v>
       </c>
-      <c r="Z25" s="3" t="n">
+      <c r="AB25" s="3" t="n">
         <v>16635.77</v>
       </c>
-      <c r="AA25" s="3" t="n">
+      <c r="AC25" s="3" t="n">
         <v>199407.87</v>
       </c>
-      <c r="AB25" s="3" t="n">
+      <c r="AD25" s="3" t="n">
         <v>37384.27</v>
       </c>
-      <c r="AC25" s="3" t="n">
+      <c r="AE25" s="3" t="n">
         <v>1405.12</v>
       </c>
     </row>
@@ -14851,28 +15007,34 @@
         <v>0</v>
       </c>
       <c r="U26" s="2" t="n">
+        <v>727.6491944960188</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="2" t="n">
         <v>1378.5</v>
       </c>
-      <c r="V26" s="2" t="inlineStr"/>
-      <c r="W26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="2" t="n">
         <v>1141481.27</v>
       </c>
-      <c r="Z26" s="2" t="n">
+      <c r="AB26" s="2" t="n">
         <v>3169.4</v>
       </c>
-      <c r="AA26" s="2" t="n">
+      <c r="AC26" s="2" t="n">
         <v>172600.05</v>
       </c>
-      <c r="AB26" s="2" t="n">
+      <c r="AD26" s="2" t="n">
         <v>35525.64</v>
       </c>
-      <c r="AC26" s="2" t="n">
+      <c r="AE26" s="2" t="n">
         <v>1414.67</v>
       </c>
     </row>
@@ -14949,33 +15111,39 @@
         <v>54324.84</v>
       </c>
       <c r="T27" s="3" t="n">
+        <v>54017.62756132293</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>307.209359888165</v>
+      </c>
+      <c r="V27" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U27" s="3" t="n">
+      <c r="W27" s="3" t="n">
         <v>2448.31</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="X27" s="3" t="n">
         <v>-9364.304182499414</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="Y27" s="3" t="n">
         <v>19412.02586288304</v>
       </c>
-      <c r="X27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3" t="n">
+      <c r="Z27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3" t="n">
         <v>1130364.75</v>
       </c>
-      <c r="Z27" s="3" t="n">
+      <c r="AB27" s="3" t="n">
         <v>17681.23</v>
       </c>
-      <c r="AA27" s="3" t="n">
+      <c r="AC27" s="3" t="n">
         <v>200577.55</v>
       </c>
-      <c r="AB27" s="3" t="n">
+      <c r="AD27" s="3" t="n">
         <v>38811.21</v>
       </c>
-      <c r="AC27" s="3" t="n">
+      <c r="AE27" s="3" t="n">
         <v>1403.44</v>
       </c>
     </row>
@@ -15055,28 +15223,34 @@
         <v>0</v>
       </c>
       <c r="U28" s="2" t="n">
+        <v>484.5271898156649</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="2" t="n">
         <v>1270.28</v>
       </c>
-      <c r="V28" s="2" t="inlineStr"/>
-      <c r="W28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X28" s="2" t="inlineStr"/>
       <c r="Y28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="2" t="n">
         <v>1143103.29</v>
       </c>
-      <c r="Z28" s="2" t="n">
+      <c r="AB28" s="2" t="n">
         <v>3683.23</v>
       </c>
-      <c r="AA28" s="2" t="n">
+      <c r="AC28" s="2" t="n">
         <v>179470.36</v>
       </c>
-      <c r="AB28" s="2" t="n">
+      <c r="AD28" s="2" t="n">
         <v>37112.51</v>
       </c>
-      <c r="AC28" s="2" t="n">
+      <c r="AE28" s="2" t="n">
         <v>1417.93</v>
       </c>
     </row>
@@ -15153,33 +15327,39 @@
         <v>49486.11</v>
       </c>
       <c r="T29" s="3" t="n">
+        <v>49029.0117571216</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>457.0936036930204</v>
+      </c>
+      <c r="V29" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="U29" s="3" t="n">
+      <c r="W29" s="3" t="n">
         <v>2265.76</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="X29" s="3" t="n">
         <v>-9465.4667806793</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="Y29" s="3" t="n">
         <v>35792.86107664475</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="n">
+      <c r="Z29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="n">
         <v>1133450.73</v>
       </c>
-      <c r="Z29" s="3" t="n">
+      <c r="AB29" s="3" t="n">
         <v>3827.24</v>
       </c>
-      <c r="AA29" s="3" t="n">
+      <c r="AC29" s="3" t="n">
         <v>218643.17</v>
       </c>
-      <c r="AB29" s="3" t="n">
+      <c r="AD29" s="3" t="n">
         <v>37400.49</v>
       </c>
-      <c r="AC29" s="3" t="n">
+      <c r="AE29" s="3" t="n">
         <v>1406.57</v>
       </c>
     </row>
@@ -15257,28 +15437,34 @@
         <v>0</v>
       </c>
       <c r="U30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="2" t="n">
         <v>1218.83</v>
       </c>
-      <c r="V30" s="2" t="inlineStr"/>
-      <c r="W30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X30" s="2" t="inlineStr"/>
       <c r="Y30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="2" t="n">
         <v>1145574.3</v>
       </c>
-      <c r="Z30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="2" t="n">
+      <c r="AB30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="2" t="n">
         <v>184854.83</v>
       </c>
-      <c r="AB30" s="2" t="n">
+      <c r="AD30" s="2" t="n">
         <v>36970.97</v>
       </c>
-      <c r="AC30" s="2" t="n">
+      <c r="AE30" s="2" t="n">
         <v>1420.97</v>
       </c>
     </row>
@@ -15353,33 +15539,39 @@
         <v>49819.31</v>
       </c>
       <c r="T31" s="3" t="n">
+        <v>49819.30691396388</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="U31" s="3" t="n">
+      <c r="W31" s="3" t="n">
         <v>2227.32</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="X31" s="3" t="n">
         <v>-9562.217152295634</v>
       </c>
-      <c r="W31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3" t="n">
         <v>1136829.73</v>
       </c>
-      <c r="Z31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="3" t="n">
+      <c r="AB31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3" t="n">
         <v>224892.59</v>
       </c>
-      <c r="AB31" s="3" t="n">
+      <c r="AD31" s="3" t="n">
         <v>36166.27</v>
       </c>
-      <c r="AC31" s="3" t="n">
+      <c r="AE31" s="3" t="n">
         <v>1408.02</v>
       </c>
     </row>
@@ -15457,28 +15649,34 @@
         <v>0</v>
       </c>
       <c r="U32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="2" t="n">
         <v>1289.58</v>
       </c>
-      <c r="V32" s="2" t="inlineStr"/>
-      <c r="W32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="2" t="n">
         <v>1143765.06</v>
       </c>
-      <c r="Z32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="2" t="n">
+      <c r="AB32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="2" t="n">
         <v>179414.52</v>
       </c>
-      <c r="AB32" s="2" t="n">
+      <c r="AD32" s="2" t="n">
         <v>35882.9</v>
       </c>
-      <c r="AC32" s="2" t="n">
+      <c r="AE32" s="2" t="n">
         <v>1419.18</v>
       </c>
     </row>
@@ -15553,33 +15751,39 @@
         <v>50032.07</v>
       </c>
       <c r="T33" s="3" t="n">
+        <v>50032.0650597966</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="U33" s="3" t="n">
+      <c r="W33" s="3" t="n">
         <v>2325.8</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="X33" s="3" t="n">
         <v>-8164.567782031372</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="Y33" s="3" t="n">
         <v>20269.44785617663</v>
       </c>
-      <c r="X33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3" t="n">
+      <c r="Z33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3" t="n">
         <v>1134024.26</v>
       </c>
-      <c r="Z33" s="3" t="n">
+      <c r="AB33" s="3" t="n">
         <v>11323.29</v>
       </c>
-      <c r="AA33" s="3" t="n">
+      <c r="AC33" s="3" t="n">
         <v>208320.62</v>
       </c>
-      <c r="AB33" s="3" t="n">
+      <c r="AD33" s="3" t="n">
         <v>38521.81</v>
       </c>
-      <c r="AC33" s="3" t="n">
+      <c r="AE33" s="3" t="n">
         <v>1406.51</v>
       </c>
     </row>
@@ -15657,28 +15861,34 @@
         <v>0</v>
       </c>
       <c r="U34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V34" s="2" t="inlineStr"/>
-      <c r="W34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X34" s="2" t="inlineStr"/>
       <c r="Y34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="2" t="n">
         <v>1386598.52</v>
       </c>
-      <c r="Z34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="2" t="n">
+      <c r="AB34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="2" t="n">
         <v>486975.02</v>
       </c>
-      <c r="AB34" s="2" t="n">
+      <c r="AD34" s="2" t="n">
         <v>97395</v>
       </c>
-      <c r="AC34" s="2" t="n">
+      <c r="AE34" s="2" t="n">
         <v>1782.93</v>
       </c>
     </row>
@@ -15756,30 +15966,36 @@
         <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3" t="n">
         <v>1386598.52</v>
       </c>
-      <c r="Z35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="3" t="n">
+      <c r="AB35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3" t="n">
         <v>486975.02</v>
       </c>
-      <c r="AB35" s="3" t="n">
+      <c r="AD35" s="3" t="n">
         <v>97395</v>
       </c>
-      <c r="AC35" s="3" t="n">
+      <c r="AE35" s="3" t="n">
         <v>1782.93</v>
       </c>
     </row>
@@ -15857,28 +16073,34 @@
         <v>0</v>
       </c>
       <c r="U36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V36" s="2" t="inlineStr"/>
-      <c r="W36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X36" s="2" t="inlineStr"/>
       <c r="Y36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="2" t="n">
         <v>1386598.52</v>
       </c>
-      <c r="Z36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="2" t="n">
+      <c r="AB36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="2" t="n">
         <v>486975.02</v>
       </c>
-      <c r="AB36" s="2" t="n">
+      <c r="AD36" s="2" t="n">
         <v>97395</v>
       </c>
-      <c r="AC36" s="2" t="n">
+      <c r="AE36" s="2" t="n">
         <v>1782.93</v>
       </c>
     </row>
@@ -15956,30 +16178,36 @@
         <v>0</v>
       </c>
       <c r="U37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="3" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="3" t="n">
         <v>1386598.52</v>
       </c>
-      <c r="Z37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="3" t="n">
+      <c r="AB37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="3" t="n">
         <v>486975.02</v>
       </c>
-      <c r="AB37" s="3" t="n">
+      <c r="AD37" s="3" t="n">
         <v>97395</v>
       </c>
-      <c r="AC37" s="3" t="n">
+      <c r="AE37" s="3" t="n">
         <v>1782.93</v>
       </c>
     </row>
@@ -16057,28 +16285,34 @@
         <v>0</v>
       </c>
       <c r="U38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V38" s="2" t="inlineStr"/>
-      <c r="W38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X38" s="2" t="inlineStr"/>
       <c r="Y38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="2" t="n">
         <v>1386598.52</v>
       </c>
-      <c r="Z38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="2" t="n">
+      <c r="AB38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="2" t="n">
         <v>486975.02</v>
       </c>
-      <c r="AB38" s="2" t="n">
+      <c r="AD38" s="2" t="n">
         <v>97395</v>
       </c>
-      <c r="AC38" s="2" t="n">
+      <c r="AE38" s="2" t="n">
         <v>1782.93</v>
       </c>
     </row>
@@ -16156,30 +16390,36 @@
         <v>0</v>
       </c>
       <c r="U39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="3" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="3" t="n">
         <v>1386598.52</v>
       </c>
-      <c r="Z39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="3" t="n">
+      <c r="AB39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="3" t="n">
         <v>486975.02</v>
       </c>
-      <c r="AB39" s="3" t="n">
+      <c r="AD39" s="3" t="n">
         <v>97395</v>
       </c>
-      <c r="AC39" s="3" t="n">
+      <c r="AE39" s="3" t="n">
         <v>1782.93</v>
       </c>
     </row>
@@ -16259,28 +16499,34 @@
         <v>0</v>
       </c>
       <c r="U40" s="2" t="n">
+        <v>257.233387444115</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="2" t="n">
         <v>1633.12</v>
       </c>
-      <c r="V40" s="2" t="inlineStr"/>
-      <c r="W40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="2" t="n">
         <v>1369471.84</v>
       </c>
-      <c r="Z40" s="2" t="n">
+      <c r="AB40" s="2" t="n">
         <v>3816.66</v>
       </c>
-      <c r="AA40" s="2" t="n">
+      <c r="AC40" s="2" t="n">
         <v>420279.57</v>
       </c>
-      <c r="AB40" s="2" t="n">
+      <c r="AD40" s="2" t="n">
         <v>85391.75</v>
       </c>
-      <c r="AC40" s="2" t="n">
+      <c r="AE40" s="2" t="n">
         <v>1757</v>
       </c>
     </row>
@@ -16357,33 +16603,39 @@
         <v>796.38</v>
       </c>
       <c r="T41" s="3" t="n">
+        <v>601.8713839681211</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>194.5079281836522</v>
+      </c>
+      <c r="V41" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="U41" s="3" t="n">
+      <c r="W41" s="3" t="n">
         <v>1645.44</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="X41" s="3" t="n">
         <v>37.13598970184103</v>
       </c>
-      <c r="W41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3" t="n">
         <v>1369385.25</v>
       </c>
-      <c r="Z41" s="3" t="n">
+      <c r="AB41" s="3" t="n">
         <v>3842.56</v>
       </c>
-      <c r="AA41" s="3" t="n">
+      <c r="AC41" s="3" t="n">
         <v>420422.11</v>
       </c>
-      <c r="AB41" s="3" t="n">
+      <c r="AD41" s="3" t="n">
         <v>85429.32000000001</v>
       </c>
-      <c r="AC41" s="3" t="n">
+      <c r="AE41" s="3" t="n">
         <v>1757.04</v>
       </c>
     </row>
@@ -16463,28 +16715,34 @@
         <v>0</v>
       </c>
       <c r="U42" s="2" t="n">
+        <v>55.20136276254334</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="2" t="n">
         <v>1445.48</v>
       </c>
-      <c r="V42" s="2" t="inlineStr"/>
-      <c r="W42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X42" s="2" t="inlineStr"/>
       <c r="Y42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="2" t="n">
         <v>1371435.67</v>
       </c>
-      <c r="Z42" s="2" t="n">
+      <c r="AB42" s="2" t="n">
         <v>2411.37</v>
       </c>
-      <c r="AA42" s="2" t="n">
+      <c r="AC42" s="2" t="n">
         <v>442205.13</v>
       </c>
-      <c r="AB42" s="2" t="n">
+      <c r="AD42" s="2" t="n">
         <v>89285</v>
       </c>
-      <c r="AC42" s="2" t="n">
+      <c r="AE42" s="2" t="n">
         <v>1759.95</v>
       </c>
     </row>
@@ -16561,33 +16819,39 @@
         <v>351.74</v>
       </c>
       <c r="T43" s="3" t="n">
+        <v>296.5273090511942</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>55.2171886822639</v>
+      </c>
+      <c r="V43" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U43" s="3" t="n">
+      <c r="W43" s="3" t="n">
         <v>1451.74</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="X43" s="3" t="n">
         <v>-61.64798964932561</v>
       </c>
-      <c r="W43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3" t="n">
         <v>1371331.3</v>
       </c>
-      <c r="Z43" s="3" t="n">
+      <c r="AB43" s="3" t="n">
         <v>2407.82</v>
       </c>
-      <c r="AA43" s="3" t="n">
+      <c r="AC43" s="3" t="n">
         <v>442227.02</v>
       </c>
-      <c r="AB43" s="3" t="n">
+      <c r="AD43" s="3" t="n">
         <v>89288.14</v>
       </c>
-      <c r="AC43" s="3" t="n">
+      <c r="AE43" s="3" t="n">
         <v>1759.88</v>
       </c>
     </row>
@@ -16667,28 +16931,34 @@
         <v>0</v>
       </c>
       <c r="U44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="2" t="n">
         <v>1284.98</v>
       </c>
-      <c r="V44" s="2" t="inlineStr"/>
-      <c r="W44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X44" s="2" t="inlineStr"/>
       <c r="Y44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="2" t="n">
         <v>1376264.68</v>
       </c>
-      <c r="Z44" s="2" t="n">
+      <c r="AB44" s="2" t="n">
         <v>1299.58</v>
       </c>
-      <c r="AA44" s="2" t="n">
+      <c r="AC44" s="2" t="n">
         <v>463983.43</v>
       </c>
-      <c r="AB44" s="2" t="n">
+      <c r="AD44" s="2" t="n">
         <v>93251.53999999999</v>
       </c>
-      <c r="AC44" s="2" t="n">
+      <c r="AE44" s="2" t="n">
         <v>1770.25</v>
       </c>
     </row>
@@ -16768,30 +17038,36 @@
         <v>0</v>
       </c>
       <c r="U45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3" t="n">
         <v>1284.98</v>
       </c>
-      <c r="V45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3" t="n">
         <v>1376264.68</v>
       </c>
-      <c r="Z45" s="3" t="n">
+      <c r="AB45" s="3" t="n">
         <v>1299.58</v>
       </c>
-      <c r="AA45" s="3" t="n">
+      <c r="AC45" s="3" t="n">
         <v>463983.43</v>
       </c>
-      <c r="AB45" s="3" t="n">
+      <c r="AD45" s="3" t="n">
         <v>93251.53999999999</v>
       </c>
-      <c r="AC45" s="3" t="n">
+      <c r="AE45" s="3" t="n">
         <v>1770.25</v>
       </c>
     </row>
@@ -16869,28 +17145,34 @@
         <v>0</v>
       </c>
       <c r="U46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="2" t="n">
         <v>1270.18</v>
       </c>
-      <c r="V46" s="2" t="inlineStr"/>
-      <c r="W46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X46" s="2" t="inlineStr"/>
       <c r="Y46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="2" t="n">
         <v>1377049.4</v>
       </c>
-      <c r="Z46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="2" t="n">
+      <c r="AB46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="2" t="n">
         <v>468089.19</v>
       </c>
-      <c r="AB46" s="2" t="n">
+      <c r="AD46" s="2" t="n">
         <v>93617.84</v>
       </c>
-      <c r="AC46" s="2" t="n">
+      <c r="AE46" s="2" t="n">
         <v>1770.56</v>
       </c>
     </row>
@@ -16965,33 +17247,39 @@
         <v>1729.37</v>
       </c>
       <c r="T47" s="3" t="n">
+        <v>1729.368683059407</v>
+      </c>
+      <c r="U47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="U47" s="3" t="n">
+      <c r="W47" s="3" t="n">
         <v>1306.39</v>
       </c>
-      <c r="V47" s="3" t="n">
+      <c r="X47" s="3" t="n">
         <v>954.2785418825224</v>
       </c>
-      <c r="W47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3" t="n">
         <v>1377580.34</v>
       </c>
-      <c r="Z47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="3" t="n">
+      <c r="AB47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3" t="n">
         <v>470203.77</v>
       </c>
-      <c r="AB47" s="3" t="n">
+      <c r="AD47" s="3" t="n">
         <v>94040.75</v>
       </c>
-      <c r="AC47" s="3" t="n">
+      <c r="AE47" s="3" t="n">
         <v>1770.97</v>
       </c>
     </row>
@@ -17069,28 +17357,34 @@
         <v>0</v>
       </c>
       <c r="U48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V48" s="2" t="inlineStr"/>
-      <c r="W48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X48" s="2" t="inlineStr"/>
       <c r="Y48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="2" t="n">
         <v>1386598.52</v>
       </c>
-      <c r="Z48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="2" t="n">
+      <c r="AB48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="2" t="n">
         <v>486975.02</v>
       </c>
-      <c r="AB48" s="2" t="n">
+      <c r="AD48" s="2" t="n">
         <v>97395</v>
       </c>
-      <c r="AC48" s="2" t="n">
+      <c r="AE48" s="2" t="n">
         <v>1782.93</v>
       </c>
     </row>
@@ -17168,30 +17462,36 @@
         <v>0</v>
       </c>
       <c r="U49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3" t="n">
         <v>1386598.52</v>
       </c>
-      <c r="Z49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="3" t="n">
+      <c r="AB49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3" t="n">
         <v>486975.02</v>
       </c>
-      <c r="AB49" s="3" t="n">
+      <c r="AD49" s="3" t="n">
         <v>97395</v>
       </c>
-      <c r="AC49" s="3" t="n">
+      <c r="AE49" s="3" t="n">
         <v>1782.93</v>
       </c>
     </row>
@@ -17269,28 +17569,34 @@
         <v>0</v>
       </c>
       <c r="U50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V50" s="2" t="inlineStr"/>
-      <c r="W50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X50" s="2" t="inlineStr"/>
       <c r="Y50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="2" t="n">
         <v>626285.6800000001</v>
       </c>
-      <c r="Z50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" s="2" t="n">
+      <c r="AB50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="2" t="n">
         <v>-372814.58</v>
       </c>
-      <c r="AB50" s="2" t="n">
+      <c r="AD50" s="2" t="n">
         <v>-1050</v>
       </c>
-      <c r="AC50" s="2" t="n">
+      <c r="AE50" s="2" t="n">
         <v>751.1799999999999</v>
       </c>
     </row>
@@ -17365,33 +17671,39 @@
         <v>199115.01</v>
       </c>
       <c r="T51" s="3" t="n">
+        <v>199115.0134050184</v>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="U51" s="3" t="n">
+      <c r="W51" s="3" t="n">
         <v>4558.82</v>
       </c>
-      <c r="V51" s="3" t="n">
+      <c r="X51" s="3" t="n">
         <v>10811.08575115539</v>
       </c>
-      <c r="W51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3" t="n">
         <v>637083.79</v>
       </c>
-      <c r="Z51" s="3" t="n">
+      <c r="AB51" s="3" t="n">
         <v>-4098.19</v>
       </c>
-      <c r="AA51" s="3" t="n">
+      <c r="AC51" s="3" t="n">
         <v>-155430.03</v>
       </c>
-      <c r="AB51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" s="3" t="n">
+      <c r="AD51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3" t="n">
         <v>764.16</v>
       </c>
     </row>
@@ -17469,28 +17781,34 @@
         <v>0</v>
       </c>
       <c r="U52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V52" s="2" t="inlineStr"/>
-      <c r="W52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X52" s="2" t="inlineStr"/>
       <c r="Y52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="2" t="n">
         <v>626285.6800000001</v>
       </c>
-      <c r="Z52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="2" t="n">
+      <c r="AB52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="2" t="n">
         <v>-372814.58</v>
       </c>
-      <c r="AB52" s="2" t="n">
+      <c r="AD52" s="2" t="n">
         <v>-1050</v>
       </c>
-      <c r="AC52" s="2" t="n">
+      <c r="AE52" s="2" t="n">
         <v>751.1799999999999</v>
       </c>
     </row>
@@ -17565,33 +17883,39 @@
         <v>199115.01</v>
       </c>
       <c r="T53" s="3" t="n">
+        <v>199115.0134050184</v>
+      </c>
+      <c r="U53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="U53" s="3" t="n">
+      <c r="W53" s="3" t="n">
         <v>4558.82</v>
       </c>
-      <c r="V53" s="3" t="n">
+      <c r="X53" s="3" t="n">
         <v>10811.08575115539</v>
       </c>
-      <c r="W53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3" t="n">
         <v>637083.79</v>
       </c>
-      <c r="Z53" s="3" t="n">
+      <c r="AB53" s="3" t="n">
         <v>-4098.19</v>
       </c>
-      <c r="AA53" s="3" t="n">
+      <c r="AC53" s="3" t="n">
         <v>-155430.03</v>
       </c>
-      <c r="AB53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="3" t="n">
+      <c r="AD53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3" t="n">
         <v>764.16</v>
       </c>
     </row>
@@ -17669,28 +17993,34 @@
         <v>0</v>
       </c>
       <c r="U54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V54" s="2" t="inlineStr"/>
-      <c r="W54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X54" s="2" t="inlineStr"/>
       <c r="Y54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="2" t="n">
         <v>626285.6800000001</v>
       </c>
-      <c r="Z54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="2" t="n">
+      <c r="AB54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="2" t="n">
         <v>-372814.58</v>
       </c>
-      <c r="AB54" s="2" t="n">
+      <c r="AD54" s="2" t="n">
         <v>-1050</v>
       </c>
-      <c r="AC54" s="2" t="n">
+      <c r="AE54" s="2" t="n">
         <v>751.1799999999999</v>
       </c>
     </row>
@@ -17765,33 +18095,39 @@
         <v>199115.01</v>
       </c>
       <c r="T55" s="3" t="n">
+        <v>199115.0134050184</v>
+      </c>
+      <c r="U55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="U55" s="3" t="n">
+      <c r="W55" s="3" t="n">
         <v>4558.82</v>
       </c>
-      <c r="V55" s="3" t="n">
+      <c r="X55" s="3" t="n">
         <v>10811.08575115539</v>
       </c>
-      <c r="W55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="3" t="n">
         <v>637083.79</v>
       </c>
-      <c r="Z55" s="3" t="n">
+      <c r="AB55" s="3" t="n">
         <v>-4098.19</v>
       </c>
-      <c r="AA55" s="3" t="n">
+      <c r="AC55" s="3" t="n">
         <v>-155430.03</v>
       </c>
-      <c r="AB55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" s="3" t="n">
+      <c r="AD55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="3" t="n">
         <v>764.16</v>
       </c>
     </row>
@@ -17871,28 +18207,34 @@
         <v>0</v>
       </c>
       <c r="U56" s="2" t="n">
+        <v>8653.280560693267</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="2" t="n">
         <v>1435.19</v>
       </c>
-      <c r="V56" s="2" t="inlineStr"/>
-      <c r="W56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X56" s="2" t="inlineStr"/>
       <c r="Y56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="2" t="n">
         <v>626767.42</v>
       </c>
-      <c r="Z56" s="2" t="n">
+      <c r="AB56" s="2" t="n">
         <v>-8984.709999999999</v>
       </c>
-      <c r="AA56" s="2" t="n">
+      <c r="AC56" s="2" t="n">
         <v>-355951.82</v>
       </c>
-      <c r="AB56" s="2" t="n">
+      <c r="AD56" s="2" t="n">
         <v>-570.8200000000001</v>
       </c>
-      <c r="AC56" s="2" t="n">
+      <c r="AE56" s="2" t="n">
         <v>751.76</v>
       </c>
     </row>
@@ -17969,33 +18311,39 @@
         <v>259108.19</v>
       </c>
       <c r="T57" s="3" t="n">
+        <v>255889.2568793757</v>
+      </c>
+      <c r="U57" s="3" t="n">
+        <v>3218.937023700735</v>
+      </c>
+      <c r="V57" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U57" s="3" t="n">
+      <c r="W57" s="3" t="n">
         <v>4488.65</v>
       </c>
-      <c r="V57" s="3" t="n">
+      <c r="X57" s="3" t="n">
         <v>7069.84987636283</v>
       </c>
-      <c r="W57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3" t="n">
         <v>633828.78</v>
       </c>
-      <c r="Z57" s="3" t="n">
+      <c r="AB57" s="3" t="n">
         <v>44036.61</v>
       </c>
-      <c r="AA57" s="3" t="n">
+      <c r="AC57" s="3" t="n">
         <v>-148717.26</v>
       </c>
-      <c r="AB57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="3" t="n">
+      <c r="AD57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="3" t="n">
         <v>760.25</v>
       </c>
     </row>
@@ -18075,28 +18423,34 @@
         <v>0</v>
       </c>
       <c r="U58" s="2" t="n">
+        <v>4551.786649646</v>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="2" t="n">
         <v>1278.74</v>
       </c>
-      <c r="V58" s="2" t="inlineStr"/>
-      <c r="W58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X58" s="2" t="inlineStr"/>
       <c r="Y58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="2" t="n">
         <v>626762.11</v>
       </c>
-      <c r="Z58" s="2" t="n">
+      <c r="AB58" s="2" t="n">
         <v>-5190.9</v>
       </c>
-      <c r="AA58" s="2" t="n">
+      <c r="AC58" s="2" t="n">
         <v>-362860.1</v>
       </c>
-      <c r="AB58" s="2" t="n">
+      <c r="AD58" s="2" t="n">
         <v>-946.25</v>
       </c>
-      <c r="AC58" s="2" t="n">
+      <c r="AE58" s="2" t="n">
         <v>751.76</v>
       </c>
     </row>
@@ -18173,33 +18527,39 @@
         <v>201925.72</v>
       </c>
       <c r="T59" s="3" t="n">
+        <v>201675.8358685558</v>
+      </c>
+      <c r="U59" s="3" t="n">
+        <v>249.8866007028963</v>
+      </c>
+      <c r="V59" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="U59" s="3" t="n">
+      <c r="W59" s="3" t="n">
         <v>4416.69</v>
       </c>
-      <c r="V59" s="3" t="n">
+      <c r="X59" s="3" t="n">
         <v>23992.33022877993</v>
       </c>
-      <c r="W59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3" t="n">
         <v>650725.65</v>
       </c>
-      <c r="Z59" s="3" t="n">
+      <c r="AB59" s="3" t="n">
         <v>8299.98</v>
       </c>
-      <c r="AA59" s="3" t="n">
+      <c r="AC59" s="3" t="n">
         <v>-151846.76</v>
       </c>
-      <c r="AB59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="3" t="n">
+      <c r="AD59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3" t="n">
         <v>780.55</v>
       </c>
     </row>
@@ -18279,28 +18639,34 @@
         <v>0</v>
       </c>
       <c r="U60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="2" t="n">
         <v>1220.22</v>
       </c>
-      <c r="V60" s="2" t="inlineStr"/>
-      <c r="W60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X60" s="2" t="inlineStr"/>
       <c r="Y60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="2" t="n">
         <v>626669.24</v>
       </c>
-      <c r="Z60" s="2" t="n">
+      <c r="AB60" s="2" t="n">
         <v>-3396.77</v>
       </c>
-      <c r="AA60" s="2" t="n">
+      <c r="AC60" s="2" t="n">
         <v>-369504.63</v>
       </c>
-      <c r="AB60" s="2" t="n">
+      <c r="AD60" s="2" t="n">
         <v>-1188.87</v>
       </c>
-      <c r="AC60" s="2" t="n">
+      <c r="AE60" s="2" t="n">
         <v>751.71</v>
       </c>
     </row>
@@ -18377,33 +18743,39 @@
         <v>202501.28</v>
       </c>
       <c r="T61" s="3" t="n">
+        <v>202501.2785317157</v>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="U61" s="3" t="n">
+      <c r="W61" s="3" t="n">
         <v>4630.49</v>
       </c>
-      <c r="V61" s="3" t="n">
+      <c r="X61" s="3" t="n">
         <v>10714.06851288362</v>
       </c>
-      <c r="W61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3" t="n">
         <v>637422.03</v>
       </c>
-      <c r="Z61" s="3" t="n">
+      <c r="AB61" s="3" t="n">
         <v>-4155.71</v>
       </c>
-      <c r="AA61" s="3" t="n">
+      <c r="AC61" s="3" t="n">
         <v>-152120.07</v>
       </c>
-      <c r="AB61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3" t="n">
+      <c r="AD61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3" t="n">
         <v>764.5599999999999</v>
       </c>
     </row>
@@ -18481,28 +18853,34 @@
         <v>0</v>
       </c>
       <c r="U62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V62" s="2" t="inlineStr"/>
-      <c r="W62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X62" s="2" t="inlineStr"/>
       <c r="Y62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="2" t="n">
         <v>626285.6800000001</v>
       </c>
-      <c r="Z62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="2" t="n">
+      <c r="AB62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="2" t="n">
         <v>-372814.58</v>
       </c>
-      <c r="AB62" s="2" t="n">
+      <c r="AD62" s="2" t="n">
         <v>-1050</v>
       </c>
-      <c r="AC62" s="2" t="n">
+      <c r="AE62" s="2" t="n">
         <v>751.1799999999999</v>
       </c>
     </row>
@@ -18577,33 +18955,39 @@
         <v>199115.01</v>
       </c>
       <c r="T63" s="3" t="n">
+        <v>199115.0134050184</v>
+      </c>
+      <c r="U63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="U63" s="3" t="n">
+      <c r="W63" s="3" t="n">
         <v>4558.82</v>
       </c>
-      <c r="V63" s="3" t="n">
+      <c r="X63" s="3" t="n">
         <v>10811.08575115539</v>
       </c>
-      <c r="W63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3" t="n">
         <v>637083.79</v>
       </c>
-      <c r="Z63" s="3" t="n">
+      <c r="AB63" s="3" t="n">
         <v>-4098.19</v>
       </c>
-      <c r="AA63" s="3" t="n">
+      <c r="AC63" s="3" t="n">
         <v>-155430.03</v>
       </c>
-      <c r="AB63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" s="3" t="n">
+      <c r="AD63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3" t="n">
         <v>764.16</v>
       </c>
     </row>
@@ -18681,28 +19065,34 @@
         <v>0</v>
       </c>
       <c r="U64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V64" s="2" t="inlineStr"/>
-      <c r="W64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X64" s="2" t="inlineStr"/>
       <c r="Y64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="2" t="n">
         <v>626285.6800000001</v>
       </c>
-      <c r="Z64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" s="2" t="n">
+      <c r="AB64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="2" t="n">
         <v>-372814.58</v>
       </c>
-      <c r="AB64" s="2" t="n">
+      <c r="AD64" s="2" t="n">
         <v>-1050</v>
       </c>
-      <c r="AC64" s="2" t="n">
+      <c r="AE64" s="2" t="n">
         <v>751.1799999999999</v>
       </c>
     </row>
@@ -18777,33 +19167,39 @@
         <v>199115.01</v>
       </c>
       <c r="T65" s="3" t="n">
+        <v>199115.0134050184</v>
+      </c>
+      <c r="U65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="U65" s="3" t="n">
+      <c r="W65" s="3" t="n">
         <v>4558.82</v>
       </c>
-      <c r="V65" s="3" t="n">
+      <c r="X65" s="3" t="n">
         <v>10811.08575115539</v>
       </c>
-      <c r="W65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3" t="n">
         <v>637083.79</v>
       </c>
-      <c r="Z65" s="3" t="n">
+      <c r="AB65" s="3" t="n">
         <v>-4098.19</v>
       </c>
-      <c r="AA65" s="3" t="n">
+      <c r="AC65" s="3" t="n">
         <v>-155430.03</v>
       </c>
-      <c r="AB65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC65" s="3" t="n">
+      <c r="AD65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3" t="n">
         <v>764.16</v>
       </c>
     </row>
@@ -18881,28 +19277,34 @@
         <v>0</v>
       </c>
       <c r="U66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V66" s="2" t="inlineStr"/>
-      <c r="W66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X66" s="2" t="inlineStr"/>
       <c r="Y66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="2" t="n">
         <v>1114063.87</v>
       </c>
-      <c r="Z66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="2" t="n">
+      <c r="AB66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="2" t="n">
         <v>145794.93</v>
       </c>
-      <c r="AB66" s="2" t="n">
+      <c r="AD66" s="2" t="n">
         <v>29158.99</v>
       </c>
-      <c r="AC66" s="2" t="n">
+      <c r="AE66" s="2" t="n">
         <v>1373.52</v>
       </c>
     </row>
@@ -18977,33 +19379,39 @@
         <v>48163.87</v>
       </c>
       <c r="T67" s="3" t="n">
+        <v>48163.87026226369</v>
+      </c>
+      <c r="U67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U67" s="3" t="n">
+      <c r="W67" s="3" t="n">
         <v>2039.08</v>
       </c>
-      <c r="V67" s="3" t="n">
+      <c r="X67" s="3" t="n">
         <v>7632.829529602313</v>
       </c>
-      <c r="W67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="3" t="n">
         <v>1119154.13</v>
       </c>
-      <c r="Z67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA67" s="3" t="n">
+      <c r="AB67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="3" t="n">
         <v>201382.16</v>
       </c>
-      <c r="AB67" s="3" t="n">
+      <c r="AD67" s="3" t="n">
         <v>31693.66</v>
       </c>
-      <c r="AC67" s="3" t="n">
+      <c r="AE67" s="3" t="n">
         <v>1381.42</v>
       </c>
     </row>
@@ -19081,28 +19489,34 @@
         <v>0</v>
       </c>
       <c r="U68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V68" s="2" t="inlineStr"/>
-      <c r="W68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X68" s="2" t="inlineStr"/>
       <c r="Y68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="2" t="n">
         <v>1114063.87</v>
       </c>
-      <c r="Z68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" s="2" t="n">
+      <c r="AB68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="2" t="n">
         <v>145794.93</v>
       </c>
-      <c r="AB68" s="2" t="n">
+      <c r="AD68" s="2" t="n">
         <v>29158.99</v>
       </c>
-      <c r="AC68" s="2" t="n">
+      <c r="AE68" s="2" t="n">
         <v>1373.52</v>
       </c>
     </row>
@@ -19177,33 +19591,39 @@
         <v>48163.87</v>
       </c>
       <c r="T69" s="3" t="n">
+        <v>48163.87026226369</v>
+      </c>
+      <c r="U69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U69" s="3" t="n">
+      <c r="W69" s="3" t="n">
         <v>2039.08</v>
       </c>
-      <c r="V69" s="3" t="n">
+      <c r="X69" s="3" t="n">
         <v>7632.829529602313</v>
       </c>
-      <c r="W69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3" t="n">
         <v>1119154.13</v>
       </c>
-      <c r="Z69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA69" s="3" t="n">
+      <c r="AB69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3" t="n">
         <v>201382.16</v>
       </c>
-      <c r="AB69" s="3" t="n">
+      <c r="AD69" s="3" t="n">
         <v>31693.66</v>
       </c>
-      <c r="AC69" s="3" t="n">
+      <c r="AE69" s="3" t="n">
         <v>1381.42</v>
       </c>
     </row>
@@ -19281,28 +19701,34 @@
         <v>0</v>
       </c>
       <c r="U70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V70" s="2" t="inlineStr"/>
-      <c r="W70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X70" s="2" t="inlineStr"/>
       <c r="Y70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="2" t="n">
         <v>1114063.87</v>
       </c>
-      <c r="Z70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA70" s="2" t="n">
+      <c r="AB70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="2" t="n">
         <v>145794.93</v>
       </c>
-      <c r="AB70" s="2" t="n">
+      <c r="AD70" s="2" t="n">
         <v>29158.99</v>
       </c>
-      <c r="AC70" s="2" t="n">
+      <c r="AE70" s="2" t="n">
         <v>1373.52</v>
       </c>
     </row>
@@ -19377,33 +19803,39 @@
         <v>48163.87</v>
       </c>
       <c r="T71" s="3" t="n">
+        <v>48163.87026226369</v>
+      </c>
+      <c r="U71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U71" s="3" t="n">
+      <c r="W71" s="3" t="n">
         <v>2039.08</v>
       </c>
-      <c r="V71" s="3" t="n">
+      <c r="X71" s="3" t="n">
         <v>7632.829529602313</v>
       </c>
-      <c r="W71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3" t="n">
         <v>1119154.13</v>
       </c>
-      <c r="Z71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA71" s="3" t="n">
+      <c r="AB71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3" t="n">
         <v>201382.16</v>
       </c>
-      <c r="AB71" s="3" t="n">
+      <c r="AD71" s="3" t="n">
         <v>31693.66</v>
       </c>
-      <c r="AC71" s="3" t="n">
+      <c r="AE71" s="3" t="n">
         <v>1381.42</v>
       </c>
     </row>
@@ -19483,28 +19915,34 @@
         <v>0</v>
       </c>
       <c r="U72" s="2" t="n">
+        <v>2054.4100544243</v>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="2" t="n">
         <v>1468.25</v>
       </c>
-      <c r="V72" s="2" t="inlineStr"/>
-      <c r="W72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X72" s="2" t="inlineStr"/>
       <c r="Y72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="2" t="n">
         <v>1108642.94</v>
       </c>
-      <c r="Z72" s="2" t="n">
+      <c r="AB72" s="2" t="n">
         <v>2597.11</v>
       </c>
-      <c r="AA72" s="2" t="n">
+      <c r="AC72" s="2" t="n">
         <v>133049.05</v>
       </c>
-      <c r="AB72" s="2" t="n">
+      <c r="AD72" s="2" t="n">
         <v>27518.8</v>
       </c>
-      <c r="AC72" s="2" t="n">
+      <c r="AE72" s="2" t="n">
         <v>1366.01</v>
       </c>
     </row>
@@ -19581,33 +20019,39 @@
         <v>91020.97</v>
       </c>
       <c r="T73" s="3" t="n">
+        <v>89321.93465496044</v>
+      </c>
+      <c r="U73" s="3" t="n">
+        <v>1699.036342570836</v>
+      </c>
+      <c r="V73" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="U73" s="3" t="n">
+      <c r="W73" s="3" t="n">
         <v>3146.27</v>
       </c>
-      <c r="V73" s="3" t="n">
+      <c r="X73" s="3" t="n">
         <v>-17649.09931309614</v>
       </c>
-      <c r="W73" s="3" t="n">
+      <c r="Y73" s="3" t="n">
         <v>82783.4892563381</v>
       </c>
-      <c r="X73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y73" s="3" t="n">
+      <c r="Z73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3" t="n">
         <v>1093993.01</v>
       </c>
-      <c r="Z73" s="3" t="n">
+      <c r="AB73" s="3" t="n">
         <v>4878.13</v>
       </c>
-      <c r="AA73" s="3" t="n">
+      <c r="AC73" s="3" t="n">
         <v>201207.49</v>
       </c>
-      <c r="AB73" s="3" t="n">
+      <c r="AD73" s="3" t="n">
         <v>25392.68</v>
       </c>
-      <c r="AC73" s="3" t="n">
+      <c r="AE73" s="3" t="n">
         <v>1344.83</v>
       </c>
     </row>
@@ -19687,28 +20131,34 @@
         <v>0</v>
       </c>
       <c r="U74" s="2" t="n">
+        <v>368.6994882707686</v>
+      </c>
+      <c r="V74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="2" t="n">
         <v>1340.99</v>
       </c>
-      <c r="V74" s="2" t="inlineStr"/>
-      <c r="W74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X74" s="2" t="inlineStr"/>
       <c r="Y74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="2" t="n">
         <v>1109333.7</v>
       </c>
-      <c r="Z74" s="2" t="n">
+      <c r="AB74" s="2" t="n">
         <v>1141.45</v>
       </c>
-      <c r="AA74" s="2" t="n">
+      <c r="AC74" s="2" t="n">
         <v>135460.16</v>
       </c>
-      <c r="AB74" s="2" t="n">
+      <c r="AD74" s="2" t="n">
         <v>27451.23</v>
       </c>
-      <c r="AC74" s="2" t="n">
+      <c r="AE74" s="2" t="n">
         <v>1366.15</v>
       </c>
     </row>
@@ -19785,33 +20235,39 @@
         <v>44651.32</v>
       </c>
       <c r="T75" s="3" t="n">
+        <v>44550.73466226915</v>
+      </c>
+      <c r="U75" s="3" t="n">
+        <v>100.5841132989007</v>
+      </c>
+      <c r="V75" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="U75" s="3" t="n">
+      <c r="W75" s="3" t="n">
         <v>2273.79</v>
       </c>
-      <c r="V75" s="3" t="n">
+      <c r="X75" s="3" t="n">
         <v>9283.873068445828</v>
       </c>
-      <c r="W75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3" t="n">
         <v>1107890.22</v>
       </c>
-      <c r="Z75" s="3" t="n">
+      <c r="AB75" s="3" t="n">
         <v>1061.29</v>
       </c>
-      <c r="AA75" s="3" t="n">
+      <c r="AC75" s="3" t="n">
         <v>188648.21</v>
       </c>
-      <c r="AB75" s="3" t="n">
+      <c r="AD75" s="3" t="n">
         <v>38101</v>
       </c>
-      <c r="AC75" s="3" t="n">
+      <c r="AE75" s="3" t="n">
         <v>1377.29</v>
       </c>
     </row>
@@ -19891,28 +20347,34 @@
         <v>0</v>
       </c>
       <c r="U76" s="2" t="n">
+        <v>825.0643513768264</v>
+      </c>
+      <c r="V76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="2" t="n">
         <v>1273.19</v>
       </c>
-      <c r="V76" s="2" t="inlineStr"/>
-      <c r="W76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X76" s="2" t="inlineStr"/>
       <c r="Y76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="2" t="n">
         <v>1110199.22</v>
       </c>
-      <c r="Z76" s="2" t="n">
+      <c r="AB76" s="2" t="n">
         <v>4588.38</v>
       </c>
-      <c r="AA76" s="2" t="n">
+      <c r="AC76" s="2" t="n">
         <v>137951</v>
       </c>
-      <c r="AB76" s="2" t="n">
+      <c r="AD76" s="2" t="n">
         <v>29319.89</v>
       </c>
-      <c r="AC76" s="2" t="n">
+      <c r="AE76" s="2" t="n">
         <v>1368.72</v>
       </c>
     </row>
@@ -19989,33 +20451,39 @@
         <v>50224.18</v>
       </c>
       <c r="T77" s="3" t="n">
+        <v>49365.69188702772</v>
+      </c>
+      <c r="U77" s="3" t="n">
+        <v>858.4851236015966</v>
+      </c>
+      <c r="V77" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="U77" s="3" t="n">
+      <c r="W77" s="3" t="n">
         <v>2142.1</v>
       </c>
-      <c r="V77" s="3" t="n">
+      <c r="X77" s="3" t="n">
         <v>7775.135114641394</v>
       </c>
-      <c r="W77" s="3" t="n">
+      <c r="Y77" s="3" t="n">
         <v>46122.71876668125</v>
       </c>
-      <c r="X77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y77" s="3" t="n">
+      <c r="Z77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3" t="n">
         <v>1116502.89</v>
       </c>
-      <c r="Z77" s="3" t="n">
+      <c r="AB77" s="3" t="n">
         <v>4983.21</v>
       </c>
-      <c r="AA77" s="3" t="n">
+      <c r="AC77" s="3" t="n">
         <v>194464.29</v>
       </c>
-      <c r="AB77" s="3" t="n">
+      <c r="AD77" s="3" t="n">
         <v>30793.73</v>
       </c>
-      <c r="AC77" s="3" t="n">
+      <c r="AE77" s="3" t="n">
         <v>1378.05</v>
       </c>
     </row>
@@ -20093,28 +20561,34 @@
         <v>0</v>
       </c>
       <c r="U78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="2" t="n">
         <v>1293.3</v>
       </c>
-      <c r="V78" s="2" t="inlineStr"/>
-      <c r="W78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X78" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X78" s="2" t="inlineStr"/>
       <c r="Y78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="2" t="n">
         <v>1111196.14</v>
       </c>
-      <c r="Z78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="2" t="n">
+      <c r="AB78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="2" t="n">
         <v>138809.31</v>
       </c>
-      <c r="AB78" s="2" t="n">
+      <c r="AD78" s="2" t="n">
         <v>27761.86</v>
       </c>
-      <c r="AC78" s="2" t="n">
+      <c r="AE78" s="2" t="n">
         <v>1370.21</v>
       </c>
     </row>
@@ -20189,33 +20663,39 @@
         <v>52173.28</v>
       </c>
       <c r="T79" s="3" t="n">
+        <v>52173.28437752317</v>
+      </c>
+      <c r="U79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="U79" s="3" t="n">
+      <c r="W79" s="3" t="n">
         <v>2218.72</v>
       </c>
-      <c r="V79" s="3" t="n">
+      <c r="X79" s="3" t="n">
         <v>10348.04319608957</v>
       </c>
-      <c r="W79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="3" t="n">
         <v>1117877.71</v>
       </c>
-      <c r="Z79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA79" s="3" t="n">
+      <c r="AB79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="3" t="n">
         <v>199691.79</v>
       </c>
-      <c r="AB79" s="3" t="n">
+      <c r="AD79" s="3" t="n">
         <v>31418.99</v>
       </c>
-      <c r="AC79" s="3" t="n">
+      <c r="AE79" s="3" t="n">
         <v>1379.55</v>
       </c>
     </row>
@@ -20293,28 +20773,34 @@
         <v>0</v>
       </c>
       <c r="U80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" s="2" t="n">
         <v>1264.45</v>
       </c>
-      <c r="V80" s="2" t="inlineStr"/>
-      <c r="W80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X80" s="2" t="inlineStr"/>
       <c r="Y80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="2" t="n">
         <v>1111047.86</v>
       </c>
-      <c r="Z80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="2" t="n">
+      <c r="AB80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="2" t="n">
         <v>140280.01</v>
       </c>
-      <c r="AB80" s="2" t="n">
+      <c r="AD80" s="2" t="n">
         <v>28056</v>
       </c>
-      <c r="AC80" s="2" t="n">
+      <c r="AE80" s="2" t="n">
         <v>1369.51</v>
       </c>
     </row>
@@ -20389,33 +20875,39 @@
         <v>50914.28</v>
       </c>
       <c r="T81" s="3" t="n">
+        <v>50914.2781269569</v>
+      </c>
+      <c r="U81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="U81" s="3" t="n">
+      <c r="W81" s="3" t="n">
         <v>2164.1</v>
       </c>
-      <c r="V81" s="3" t="n">
+      <c r="X81" s="3" t="n">
         <v>8880.930793539388</v>
       </c>
-      <c r="W81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3" t="n">
         <v>1116832.66</v>
       </c>
-      <c r="Z81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="3" t="n">
+      <c r="AB81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="3" t="n">
         <v>199139.91</v>
       </c>
-      <c r="AB81" s="3" t="n">
+      <c r="AD81" s="3" t="n">
         <v>31143.68</v>
       </c>
-      <c r="AC81" s="3" t="n">
+      <c r="AE81" s="3" t="n">
         <v>1377.97</v>
       </c>
     </row>
@@ -20493,28 +20985,34 @@
         <v>0</v>
       </c>
       <c r="U82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" s="2" t="n">
         <v>1371.52</v>
       </c>
-      <c r="V82" s="2" t="inlineStr"/>
-      <c r="W82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X82" s="2" t="inlineStr"/>
       <c r="Y82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="2" t="n">
         <v>1296341.04</v>
       </c>
-      <c r="Z82" s="2" t="n">
+      <c r="AB82" s="2" t="n">
         <v>-4930.55</v>
       </c>
-      <c r="AA82" s="2" t="n">
+      <c r="AC82" s="2" t="n">
         <v>354361.21</v>
       </c>
-      <c r="AB82" s="2" t="n">
+      <c r="AD82" s="2" t="n">
         <v>69886.13</v>
       </c>
-      <c r="AC82" s="2" t="n">
+      <c r="AE82" s="2" t="n">
         <v>1647.39</v>
       </c>
     </row>
@@ -20592,30 +21090,36 @@
         <v>0</v>
       </c>
       <c r="U83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3" t="n">
         <v>1371.52</v>
       </c>
-      <c r="V83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3" t="n">
         <v>1296341.04</v>
       </c>
-      <c r="Z83" s="3" t="n">
+      <c r="AB83" s="3" t="n">
         <v>-4930.55</v>
       </c>
-      <c r="AA83" s="3" t="n">
+      <c r="AC83" s="3" t="n">
         <v>354361.21</v>
       </c>
-      <c r="AB83" s="3" t="n">
+      <c r="AD83" s="3" t="n">
         <v>69886.13</v>
       </c>
-      <c r="AC83" s="3" t="n">
+      <c r="AE83" s="3" t="n">
         <v>1647.39</v>
       </c>
     </row>
@@ -20693,28 +21197,34 @@
         <v>0</v>
       </c>
       <c r="U84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V84" s="2" t="inlineStr"/>
-      <c r="W84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X84" s="2" t="inlineStr"/>
       <c r="Y84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="2" t="n">
         <v>1301064.81</v>
       </c>
-      <c r="Z84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA84" s="2" t="n">
+      <c r="AB84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="2" t="n">
         <v>379897.26</v>
       </c>
-      <c r="AB84" s="2" t="n">
+      <c r="AD84" s="2" t="n">
         <v>75979.45</v>
       </c>
-      <c r="AC84" s="2" t="n">
+      <c r="AE84" s="2" t="n">
         <v>1654.44</v>
       </c>
     </row>
@@ -20792,30 +21302,36 @@
         <v>0</v>
       </c>
       <c r="U85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3" t="n">
         <v>1301064.81</v>
       </c>
-      <c r="Z85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA85" s="3" t="n">
+      <c r="AB85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3" t="n">
         <v>379897.26</v>
       </c>
-      <c r="AB85" s="3" t="n">
+      <c r="AD85" s="3" t="n">
         <v>75979.45</v>
       </c>
-      <c r="AC85" s="3" t="n">
+      <c r="AE85" s="3" t="n">
         <v>1654.44</v>
       </c>
     </row>
@@ -20893,28 +21409,34 @@
         <v>0</v>
       </c>
       <c r="U86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V86" s="2" t="inlineStr"/>
-      <c r="W86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X86" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X86" s="2" t="inlineStr"/>
       <c r="Y86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="2" t="n">
         <v>1301064.81</v>
       </c>
-      <c r="Z86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA86" s="2" t="n">
+      <c r="AB86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="2" t="n">
         <v>379897.26</v>
       </c>
-      <c r="AB86" s="2" t="n">
+      <c r="AD86" s="2" t="n">
         <v>75979.45</v>
       </c>
-      <c r="AC86" s="2" t="n">
+      <c r="AE86" s="2" t="n">
         <v>1654.44</v>
       </c>
     </row>
@@ -20992,30 +21514,36 @@
         <v>0</v>
       </c>
       <c r="U87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X87" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3" t="n">
         <v>1301064.81</v>
       </c>
-      <c r="Z87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA87" s="3" t="n">
+      <c r="AB87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3" t="n">
         <v>379897.26</v>
       </c>
-      <c r="AB87" s="3" t="n">
+      <c r="AD87" s="3" t="n">
         <v>75979.45</v>
       </c>
-      <c r="AC87" s="3" t="n">
+      <c r="AE87" s="3" t="n">
         <v>1654.44</v>
       </c>
     </row>
@@ -21095,28 +21623,34 @@
         <v>0</v>
       </c>
       <c r="U88" s="2" t="n">
+        <v>252.7698363395181</v>
+      </c>
+      <c r="V88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" s="2" t="n">
         <v>1509.28</v>
       </c>
-      <c r="V88" s="2" t="inlineStr"/>
-      <c r="W88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X88" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X88" s="2" t="inlineStr"/>
       <c r="Y88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="2" t="n">
         <v>1290563.56</v>
       </c>
-      <c r="Z88" s="2" t="n">
+      <c r="AB88" s="2" t="n">
         <v>-1606.18</v>
       </c>
-      <c r="AA88" s="2" t="n">
+      <c r="AC88" s="2" t="n">
         <v>340660.12</v>
       </c>
-      <c r="AB88" s="2" t="n">
+      <c r="AD88" s="2" t="n">
         <v>67717.08</v>
       </c>
-      <c r="AC88" s="2" t="n">
+      <c r="AE88" s="2" t="n">
         <v>1638</v>
       </c>
     </row>
@@ -21193,33 +21727,39 @@
         <v>366.22</v>
       </c>
       <c r="T89" s="3" t="n">
+        <v>246.7098242233383</v>
+      </c>
+      <c r="U89" s="3" t="n">
+        <v>119.5055368863698</v>
+      </c>
+      <c r="V89" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U89" s="3" t="n">
+      <c r="W89" s="3" t="n">
         <v>1514.45</v>
       </c>
-      <c r="V89" s="3" t="n">
+      <c r="X89" s="3" t="n">
         <v>28.83201937796548</v>
       </c>
-      <c r="W89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3" t="n">
         <v>1290574.01</v>
       </c>
-      <c r="Z89" s="3" t="n">
+      <c r="AB89" s="3" t="n">
         <v>-1607.88</v>
       </c>
-      <c r="AA89" s="3" t="n">
+      <c r="AC89" s="3" t="n">
         <v>340655.69</v>
       </c>
-      <c r="AB89" s="3" t="n">
+      <c r="AD89" s="3" t="n">
         <v>67703.06</v>
       </c>
-      <c r="AC89" s="3" t="n">
+      <c r="AE89" s="3" t="n">
         <v>1638.03</v>
       </c>
     </row>
@@ -21299,28 +21839,34 @@
         <v>0</v>
       </c>
       <c r="U90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="2" t="n">
         <v>1354.05</v>
       </c>
-      <c r="V90" s="2" t="inlineStr"/>
-      <c r="W90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X90" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X90" s="2" t="inlineStr"/>
       <c r="Y90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="2" t="n">
         <v>1291941.99</v>
       </c>
-      <c r="Z90" s="2" t="n">
+      <c r="AB90" s="2" t="n">
         <v>-1011.65</v>
       </c>
-      <c r="AA90" s="2" t="n">
+      <c r="AC90" s="2" t="n">
         <v>357074.26</v>
       </c>
-      <c r="AB90" s="2" t="n">
+      <c r="AD90" s="2" t="n">
         <v>71121.52</v>
       </c>
-      <c r="AC90" s="2" t="n">
+      <c r="AE90" s="2" t="n">
         <v>1640.08</v>
       </c>
     </row>
@@ -21400,30 +21946,36 @@
         <v>0</v>
       </c>
       <c r="U91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="n">
         <v>1354.05</v>
       </c>
-      <c r="V91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X91" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="n">
         <v>1291941.99</v>
       </c>
-      <c r="Z91" s="3" t="n">
+      <c r="AB91" s="3" t="n">
         <v>-1011.65</v>
       </c>
-      <c r="AA91" s="3" t="n">
+      <c r="AC91" s="3" t="n">
         <v>357074.26</v>
       </c>
-      <c r="AB91" s="3" t="n">
+      <c r="AD91" s="3" t="n">
         <v>71121.52</v>
       </c>
-      <c r="AC91" s="3" t="n">
+      <c r="AE91" s="3" t="n">
         <v>1640.08</v>
       </c>
     </row>
@@ -21503,28 +22055,34 @@
         <v>0</v>
       </c>
       <c r="U92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" s="2" t="n">
         <v>1267.38</v>
       </c>
-      <c r="V92" s="2" t="inlineStr"/>
-      <c r="W92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X92" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X92" s="2" t="inlineStr"/>
       <c r="Y92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="2" t="n">
         <v>1294937.51</v>
       </c>
-      <c r="Z92" s="2" t="n">
+      <c r="AB92" s="2" t="n">
         <v>422.84</v>
       </c>
-      <c r="AA92" s="2" t="n">
+      <c r="AC92" s="2" t="n">
         <v>367433.93</v>
       </c>
-      <c r="AB92" s="2" t="n">
+      <c r="AD92" s="2" t="n">
         <v>73634.78</v>
       </c>
-      <c r="AC92" s="2" t="n">
+      <c r="AE92" s="2" t="n">
         <v>1646.61</v>
       </c>
     </row>
@@ -21604,30 +22162,36 @@
         <v>0</v>
       </c>
       <c r="U93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3" t="n">
         <v>1267.38</v>
       </c>
-      <c r="V93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3" t="n">
         <v>1294937.51</v>
       </c>
-      <c r="Z93" s="3" t="n">
+      <c r="AB93" s="3" t="n">
         <v>422.84</v>
       </c>
-      <c r="AA93" s="3" t="n">
+      <c r="AC93" s="3" t="n">
         <v>367433.93</v>
       </c>
-      <c r="AB93" s="3" t="n">
+      <c r="AD93" s="3" t="n">
         <v>73634.78</v>
       </c>
-      <c r="AC93" s="3" t="n">
+      <c r="AE93" s="3" t="n">
         <v>1646.61</v>
       </c>
     </row>
@@ -21705,28 +22269,34 @@
         <v>0</v>
       </c>
       <c r="U94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V94" s="2" t="inlineStr"/>
-      <c r="W94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X94" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X94" s="2" t="inlineStr"/>
       <c r="Y94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="2" t="n">
         <v>1301064.81</v>
       </c>
-      <c r="Z94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="2" t="n">
+      <c r="AB94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="2" t="n">
         <v>379897.26</v>
       </c>
-      <c r="AB94" s="2" t="n">
+      <c r="AD94" s="2" t="n">
         <v>75979.45</v>
       </c>
-      <c r="AC94" s="2" t="n">
+      <c r="AE94" s="2" t="n">
         <v>1654.44</v>
       </c>
     </row>
@@ -21804,30 +22374,36 @@
         <v>0</v>
       </c>
       <c r="U95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="3" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W95" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X95" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="3" t="n">
         <v>1301064.81</v>
       </c>
-      <c r="Z95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA95" s="3" t="n">
+      <c r="AB95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="3" t="n">
         <v>379897.26</v>
       </c>
-      <c r="AB95" s="3" t="n">
+      <c r="AD95" s="3" t="n">
         <v>75979.45</v>
       </c>
-      <c r="AC95" s="3" t="n">
+      <c r="AE95" s="3" t="n">
         <v>1654.44</v>
       </c>
     </row>
@@ -21905,28 +22481,34 @@
         <v>0</v>
       </c>
       <c r="U96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V96" s="2" t="inlineStr"/>
-      <c r="W96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X96" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X96" s="2" t="inlineStr"/>
       <c r="Y96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="2" t="n">
         <v>1301064.81</v>
       </c>
-      <c r="Z96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="2" t="n">
+      <c r="AB96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="2" t="n">
         <v>379897.26</v>
       </c>
-      <c r="AB96" s="2" t="n">
+      <c r="AD96" s="2" t="n">
         <v>75979.45</v>
       </c>
-      <c r="AC96" s="2" t="n">
+      <c r="AE96" s="2" t="n">
         <v>1654.44</v>
       </c>
     </row>
@@ -22004,30 +22586,36 @@
         <v>0</v>
       </c>
       <c r="U97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X97" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3" t="n">
         <v>1301064.81</v>
       </c>
-      <c r="Z97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA97" s="3" t="n">
+      <c r="AB97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3" t="n">
         <v>379897.26</v>
       </c>
-      <c r="AB97" s="3" t="n">
+      <c r="AD97" s="3" t="n">
         <v>75979.45</v>
       </c>
-      <c r="AC97" s="3" t="n">
+      <c r="AE97" s="3" t="n">
         <v>1654.44</v>
       </c>
     </row>
@@ -22105,28 +22693,34 @@
         <v>0</v>
       </c>
       <c r="U98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" s="2" t="n">
         <v>1727.87</v>
       </c>
-      <c r="V98" s="2" t="inlineStr"/>
-      <c r="W98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X98" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X98" s="2" t="inlineStr"/>
       <c r="Y98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="2" t="n">
         <v>1027869.74</v>
       </c>
-      <c r="Z98" s="2" t="n">
+      <c r="AB98" s="2" t="n">
         <v>-12360.93</v>
       </c>
-      <c r="AA98" s="2" t="n">
+      <c r="AC98" s="2" t="n">
         <v>10694.88</v>
       </c>
-      <c r="AB98" s="2" t="n">
+      <c r="AD98" s="2" t="n">
         <v>-2187.35</v>
       </c>
-      <c r="AC98" s="2" t="n">
+      <c r="AE98" s="2" t="n">
         <v>1245.74</v>
       </c>
     </row>
@@ -22201,33 +22795,39 @@
         <v>178330.8</v>
       </c>
       <c r="T99" s="3" t="n">
+        <v>178330.8000481078</v>
+      </c>
+      <c r="U99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="U99" s="3" t="n">
+      <c r="W99" s="3" t="n">
         <v>4333.02</v>
       </c>
-      <c r="V99" s="3" t="n">
+      <c r="X99" s="3" t="n">
         <v>2813.34794017754</v>
       </c>
-      <c r="W99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X99" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3" t="n">
         <v>1030631.53</v>
       </c>
-      <c r="Z99" s="3" t="n">
+      <c r="AB99" s="3" t="n">
         <v>24788.43</v>
       </c>
-      <c r="AA99" s="3" t="n">
+      <c r="AC99" s="3" t="n">
         <v>157885.2</v>
       </c>
-      <c r="AB99" s="3" t="n">
+      <c r="AD99" s="3" t="n">
         <v>10103.42</v>
       </c>
-      <c r="AC99" s="3" t="n">
+      <c r="AE99" s="3" t="n">
         <v>1249.12</v>
       </c>
     </row>
@@ -22305,28 +22905,34 @@
         <v>0</v>
       </c>
       <c r="U100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" s="2" t="n">
         <v>1469.77</v>
       </c>
-      <c r="V100" s="2" t="inlineStr"/>
-      <c r="W100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X100" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X100" s="2" t="inlineStr"/>
       <c r="Y100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="2" t="n">
         <v>1039453.51</v>
       </c>
-      <c r="Z100" s="2" t="n">
+      <c r="AB100" s="2" t="n">
         <v>-15606.57</v>
       </c>
-      <c r="AA100" s="2" t="n">
+      <c r="AC100" s="2" t="n">
         <v>43608.56</v>
       </c>
-      <c r="AB100" s="2" t="n">
+      <c r="AD100" s="2" t="n">
         <v>5600.4</v>
       </c>
-      <c r="AC100" s="2" t="n">
+      <c r="AE100" s="2" t="n">
         <v>1261.51</v>
       </c>
     </row>
@@ -22401,33 +23007,39 @@
         <v>152622.52</v>
       </c>
       <c r="T101" s="3" t="n">
+        <v>152622.5151233488</v>
+      </c>
+      <c r="U101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="U101" s="3" t="n">
+      <c r="W101" s="3" t="n">
         <v>3940.95</v>
       </c>
-      <c r="V101" s="3" t="n">
+      <c r="X101" s="3" t="n">
         <v>3407.225095171714</v>
       </c>
-      <c r="W101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3" t="n">
         <v>1041680.96</v>
       </c>
-      <c r="Z101" s="3" t="n">
+      <c r="AB101" s="3" t="n">
         <v>-3655.51</v>
       </c>
-      <c r="AA101" s="3" t="n">
+      <c r="AC101" s="3" t="n">
         <v>190686.61</v>
       </c>
-      <c r="AB101" s="3" t="n">
+      <c r="AD101" s="3" t="n">
         <v>12771.88</v>
       </c>
-      <c r="AC101" s="3" t="n">
+      <c r="AE101" s="3" t="n">
         <v>1265.6</v>
       </c>
     </row>
@@ -22505,28 +23117,34 @@
         <v>0</v>
       </c>
       <c r="U102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V102" s="2" t="inlineStr"/>
-      <c r="W102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X102" s="2" t="inlineStr"/>
       <c r="Y102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="2" t="n">
         <v>1060342.64</v>
       </c>
-      <c r="Z102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="2" t="n">
+      <c r="AB102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="2" t="n">
         <v>78542.50999999999</v>
       </c>
-      <c r="AB102" s="2" t="n">
+      <c r="AD102" s="2" t="n">
         <v>15708.5</v>
       </c>
-      <c r="AC102" s="2" t="n">
+      <c r="AE102" s="2" t="n">
         <v>1292.81</v>
       </c>
     </row>
@@ -22601,33 +23219,39 @@
         <v>158624.65</v>
       </c>
       <c r="T103" s="3" t="n">
+        <v>158624.6454586434</v>
+      </c>
+      <c r="U103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="U103" s="3" t="n">
+      <c r="W103" s="3" t="n">
         <v>4059.74</v>
       </c>
-      <c r="V103" s="3" t="n">
+      <c r="X103" s="3" t="n">
         <v>8219.220930879237</v>
       </c>
-      <c r="W103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X103" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="3" t="n">
         <v>1066335.91</v>
       </c>
-      <c r="Z103" s="3" t="n">
+      <c r="AB103" s="3" t="n">
         <v>23616.13</v>
       </c>
-      <c r="AA103" s="3" t="n">
+      <c r="AC103" s="3" t="n">
         <v>224631.43</v>
       </c>
-      <c r="AB103" s="3" t="n">
+      <c r="AD103" s="3" t="n">
         <v>18974.58</v>
       </c>
-      <c r="AC103" s="3" t="n">
+      <c r="AE103" s="3" t="n">
         <v>1302.68</v>
       </c>
     </row>
@@ -22707,28 +23331,34 @@
         <v>0</v>
       </c>
       <c r="U104" s="2" t="n">
+        <v>5018.893461782074</v>
+      </c>
+      <c r="V104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="2" t="n">
         <v>2158.4</v>
       </c>
-      <c r="V104" s="2" t="inlineStr"/>
-      <c r="W104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X104" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X104" s="2" t="inlineStr"/>
       <c r="Y104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="2" t="n">
         <v>1025305.76</v>
       </c>
-      <c r="Z104" s="2" t="n">
+      <c r="AB104" s="2" t="n">
         <v>-15408.82</v>
       </c>
-      <c r="AA104" s="2" t="n">
+      <c r="AC104" s="2" t="n">
         <v>10306.78</v>
       </c>
-      <c r="AB104" s="2" t="n">
+      <c r="AD104" s="2" t="n">
         <v>-1458.51</v>
       </c>
-      <c r="AC104" s="2" t="n">
+      <c r="AE104" s="2" t="n">
         <v>1239.83</v>
       </c>
     </row>
@@ -22805,33 +23435,39 @@
         <v>151745.6</v>
       </c>
       <c r="T105" s="3" t="n">
+        <v>149879.0309312511</v>
+      </c>
+      <c r="U105" s="3" t="n">
+        <v>1866.571235687303</v>
+      </c>
+      <c r="V105" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="U105" s="3" t="n">
+      <c r="W105" s="3" t="n">
         <v>4772.51</v>
       </c>
-      <c r="V105" s="3" t="n">
+      <c r="X105" s="3" t="n">
         <v>-2261.97215115244</v>
       </c>
-      <c r="W105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X105" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="3" t="n">
         <v>1023265.89</v>
       </c>
-      <c r="Z105" s="3" t="n">
+      <c r="AB105" s="3" t="n">
         <v>-13910.26</v>
       </c>
-      <c r="AA105" s="3" t="n">
+      <c r="AC105" s="3" t="n">
         <v>155020.72</v>
       </c>
-      <c r="AB105" s="3" t="n">
+      <c r="AD105" s="3" t="n">
         <v>7477.8</v>
       </c>
-      <c r="AC105" s="3" t="n">
+      <c r="AE105" s="3" t="n">
         <v>1237.12</v>
       </c>
     </row>
@@ -22911,28 +23547,34 @@
         <v>0</v>
       </c>
       <c r="U106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="2" t="n">
         <v>1586.14</v>
       </c>
-      <c r="V106" s="2" t="inlineStr"/>
-      <c r="W106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X106" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X106" s="2" t="inlineStr"/>
       <c r="Y106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="2" t="n">
         <v>1029541.11</v>
       </c>
-      <c r="Z106" s="2" t="n">
+      <c r="AB106" s="2" t="n">
         <v>-30613.2</v>
       </c>
-      <c r="AA106" s="2" t="n">
+      <c r="AC106" s="2" t="n">
         <v>46084.06</v>
       </c>
-      <c r="AB106" s="2" t="n">
+      <c r="AD106" s="2" t="n">
         <v>1852.89</v>
       </c>
-      <c r="AC106" s="2" t="n">
+      <c r="AE106" s="2" t="n">
         <v>1245.62</v>
       </c>
     </row>
@@ -23009,33 +23651,39 @@
         <v>184313.59</v>
       </c>
       <c r="T107" s="3" t="n">
+        <v>184313.5926386287</v>
+      </c>
+      <c r="U107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="U107" s="3" t="n">
+      <c r="W107" s="3" t="n">
         <v>4994.23</v>
       </c>
-      <c r="V107" s="3" t="n">
+      <c r="X107" s="3" t="n">
         <v>7770.03427837987</v>
       </c>
-      <c r="W107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X107" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="3" t="n">
         <v>1035066.19</v>
       </c>
-      <c r="Z107" s="3" t="n">
+      <c r="AB107" s="3" t="n">
         <v>17770.49</v>
       </c>
-      <c r="AA107" s="3" t="n">
+      <c r="AC107" s="3" t="n">
         <v>193243.18</v>
       </c>
-      <c r="AB107" s="3" t="n">
+      <c r="AD107" s="3" t="n">
         <v>10517.72</v>
       </c>
-      <c r="AC107" s="3" t="n">
+      <c r="AE107" s="3" t="n">
         <v>1254.95</v>
       </c>
     </row>
@@ -23115,28 +23763,34 @@
         <v>0</v>
       </c>
       <c r="U108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="2" t="n">
         <v>1332.03</v>
       </c>
-      <c r="V108" s="2" t="inlineStr"/>
-      <c r="W108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X108" s="2" t="inlineStr"/>
       <c r="Y108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="2" t="n">
         <v>1050944.36</v>
       </c>
-      <c r="Z108" s="2" t="n">
+      <c r="AB108" s="2" t="n">
         <v>-9263.75</v>
       </c>
-      <c r="AA108" s="2" t="n">
+      <c r="AC108" s="2" t="n">
         <v>61555.79</v>
       </c>
-      <c r="AB108" s="2" t="n">
+      <c r="AD108" s="2" t="n">
         <v>9068.84</v>
       </c>
-      <c r="AC108" s="2" t="n">
+      <c r="AE108" s="2" t="n">
         <v>1280.23</v>
       </c>
     </row>
@@ -23213,33 +23867,39 @@
         <v>174548.18</v>
       </c>
       <c r="T109" s="3" t="n">
+        <v>174548.1832045865</v>
+      </c>
+      <c r="U109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="U109" s="3" t="n">
+      <c r="W109" s="3" t="n">
         <v>4453.82</v>
       </c>
-      <c r="V109" s="3" t="n">
+      <c r="X109" s="3" t="n">
         <v>8212.472143219784</v>
       </c>
-      <c r="W109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X109" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="3" t="n">
         <v>1057875.2</v>
       </c>
-      <c r="Z109" s="3" t="n">
+      <c r="AB109" s="3" t="n">
         <v>30529.78</v>
       </c>
-      <c r="AA109" s="3" t="n">
+      <c r="AC109" s="3" t="n">
         <v>207644.7</v>
       </c>
-      <c r="AB109" s="3" t="n">
+      <c r="AD109" s="3" t="n">
         <v>16954.78</v>
       </c>
-      <c r="AC109" s="3" t="n">
+      <c r="AE109" s="3" t="n">
         <v>1290.08</v>
       </c>
     </row>
@@ -23317,28 +23977,34 @@
         <v>0</v>
       </c>
       <c r="U110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="2" t="n">
         <v>1578.88</v>
       </c>
-      <c r="V110" s="2" t="inlineStr"/>
-      <c r="W110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X110" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X110" s="2" t="inlineStr"/>
       <c r="Y110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="2" t="n">
         <v>1035370.9</v>
       </c>
-      <c r="Z110" s="2" t="n">
+      <c r="AB110" s="2" t="n">
         <v>-17680.87</v>
       </c>
-      <c r="AA110" s="2" t="n">
+      <c r="AC110" s="2" t="n">
         <v>30553.83</v>
       </c>
-      <c r="AB110" s="2" t="n">
+      <c r="AD110" s="2" t="n">
         <v>-77.54000000000001</v>
       </c>
-      <c r="AC110" s="2" t="n">
+      <c r="AE110" s="2" t="n">
         <v>1256.19</v>
       </c>
     </row>
@@ -23413,33 +24079,39 @@
         <v>157623.2</v>
       </c>
       <c r="T111" s="3" t="n">
+        <v>157623.1968069129</v>
+      </c>
+      <c r="U111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="U111" s="3" t="n">
+      <c r="W111" s="3" t="n">
         <v>4278.09</v>
       </c>
-      <c r="V111" s="3" t="n">
+      <c r="X111" s="3" t="n">
         <v>4621.768885272671</v>
       </c>
-      <c r="W111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X111" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="3" t="n">
         <v>1039036.92</v>
       </c>
-      <c r="Z111" s="3" t="n">
+      <c r="AB111" s="3" t="n">
         <v>621.71</v>
       </c>
-      <c r="AA111" s="3" t="n">
+      <c r="AC111" s="3" t="n">
         <v>177866.93</v>
       </c>
-      <c r="AB111" s="3" t="n">
+      <c r="AD111" s="3" t="n">
         <v>12194.19</v>
       </c>
-      <c r="AC111" s="3" t="n">
+      <c r="AE111" s="3" t="n">
         <v>1261.73</v>
       </c>
     </row>
@@ -23517,28 +24189,34 @@
         <v>0</v>
       </c>
       <c r="U112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="2" t="n">
         <v>1576.98</v>
       </c>
-      <c r="V112" s="2" t="inlineStr"/>
-      <c r="W112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X112" s="2" t="inlineStr"/>
       <c r="Y112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" s="2" t="n">
         <v>1060415.34</v>
       </c>
-      <c r="Z112" s="2" t="n">
+      <c r="AB112" s="2" t="n">
         <v>30870.94</v>
       </c>
-      <c r="AA112" s="2" t="n">
+      <c r="AC112" s="2" t="n">
         <v>28676.35</v>
       </c>
-      <c r="AB112" s="2" t="n">
+      <c r="AD112" s="2" t="n">
         <v>16540.1</v>
       </c>
-      <c r="AC112" s="2" t="n">
+      <c r="AE112" s="2" t="n">
         <v>1299.99</v>
       </c>
     </row>
@@ -23613,33 +24291,39 @@
         <v>122522.46</v>
       </c>
       <c r="T113" s="3" t="n">
+        <v>122522.4630459374</v>
+      </c>
+      <c r="U113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="U113" s="3" t="n">
+      <c r="W113" s="3" t="n">
         <v>3853.93</v>
       </c>
-      <c r="V113" s="3" t="n">
+      <c r="X113" s="3" t="n">
         <v>695.6735842826311</v>
       </c>
-      <c r="W113" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" s="3" t="n">
         <v>1065146.29</v>
       </c>
-      <c r="Z113" s="3" t="n">
+      <c r="AB113" s="3" t="n">
         <v>9560.799999999999</v>
       </c>
-      <c r="AA113" s="3" t="n">
+      <c r="AC113" s="3" t="n">
         <v>176223.99</v>
       </c>
-      <c r="AB113" s="3" t="n">
+      <c r="AD113" s="3" t="n">
         <v>18625.26</v>
       </c>
-      <c r="AC113" s="3" t="n">
+      <c r="AE113" s="3" t="n">
         <v>1300.83</v>
       </c>
     </row>
@@ -23717,28 +24401,34 @@
         <v>0</v>
       </c>
       <c r="U114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V114" s="2" t="inlineStr"/>
-      <c r="W114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X114" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X114" s="2" t="inlineStr"/>
       <c r="Y114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="2" t="n">
         <v>1124315.52</v>
       </c>
-      <c r="Z114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA114" s="2" t="n">
+      <c r="AB114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" s="2" t="n">
         <v>158628.74</v>
       </c>
-      <c r="AB114" s="2" t="n">
+      <c r="AD114" s="2" t="n">
         <v>31725.75</v>
       </c>
-      <c r="AC114" s="2" t="n">
+      <c r="AE114" s="2" t="n">
         <v>1388.92</v>
       </c>
     </row>
@@ -23813,33 +24503,39 @@
         <v>40414</v>
       </c>
       <c r="T115" s="3" t="n">
+        <v>40413.99704287824</v>
+      </c>
+      <c r="U115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U115" s="3" t="n">
+      <c r="W115" s="3" t="n">
         <v>2060.53</v>
       </c>
-      <c r="V115" s="3" t="n">
+      <c r="X115" s="3" t="n">
         <v>4797.722615555162</v>
       </c>
-      <c r="W115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X115" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="3" t="n">
         <v>1127136.8</v>
       </c>
-      <c r="Z115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA115" s="3" t="n">
+      <c r="AB115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" s="3" t="n">
         <v>203652.43</v>
       </c>
-      <c r="AB115" s="3" t="n">
+      <c r="AD115" s="3" t="n">
         <v>33697.69</v>
       </c>
-      <c r="AC115" s="3" t="n">
+      <c r="AE115" s="3" t="n">
         <v>1393.41</v>
       </c>
     </row>
@@ -23917,28 +24613,34 @@
         <v>0</v>
       </c>
       <c r="U116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V116" s="2" t="inlineStr"/>
-      <c r="W116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X116" s="2" t="inlineStr"/>
       <c r="Y116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="2" t="n">
         <v>1124315.52</v>
       </c>
-      <c r="Z116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA116" s="2" t="n">
+      <c r="AB116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="2" t="n">
         <v>158628.74</v>
       </c>
-      <c r="AB116" s="2" t="n">
+      <c r="AD116" s="2" t="n">
         <v>31725.75</v>
       </c>
-      <c r="AC116" s="2" t="n">
+      <c r="AE116" s="2" t="n">
         <v>1388.92</v>
       </c>
     </row>
@@ -24013,33 +24715,39 @@
         <v>40414</v>
       </c>
       <c r="T117" s="3" t="n">
+        <v>40413.99704287824</v>
+      </c>
+      <c r="U117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U117" s="3" t="n">
+      <c r="W117" s="3" t="n">
         <v>2060.53</v>
       </c>
-      <c r="V117" s="3" t="n">
+      <c r="X117" s="3" t="n">
         <v>4797.722615555162</v>
       </c>
-      <c r="W117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X117" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA117" s="3" t="n">
         <v>1127136.8</v>
       </c>
-      <c r="Z117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA117" s="3" t="n">
+      <c r="AB117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC117" s="3" t="n">
         <v>203652.43</v>
       </c>
-      <c r="AB117" s="3" t="n">
+      <c r="AD117" s="3" t="n">
         <v>33697.69</v>
       </c>
-      <c r="AC117" s="3" t="n">
+      <c r="AE117" s="3" t="n">
         <v>1393.41</v>
       </c>
     </row>
@@ -24117,28 +24825,34 @@
         <v>0</v>
       </c>
       <c r="U118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V118" s="2" t="inlineStr"/>
-      <c r="W118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X118" s="2" t="inlineStr"/>
       <c r="Y118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="2" t="n">
         <v>1124315.52</v>
       </c>
-      <c r="Z118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA118" s="2" t="n">
+      <c r="AB118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC118" s="2" t="n">
         <v>158628.74</v>
       </c>
-      <c r="AB118" s="2" t="n">
+      <c r="AD118" s="2" t="n">
         <v>31725.75</v>
       </c>
-      <c r="AC118" s="2" t="n">
+      <c r="AE118" s="2" t="n">
         <v>1388.92</v>
       </c>
     </row>
@@ -24213,33 +24927,39 @@
         <v>40414</v>
       </c>
       <c r="T119" s="3" t="n">
+        <v>40413.99704287824</v>
+      </c>
+      <c r="U119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U119" s="3" t="n">
+      <c r="W119" s="3" t="n">
         <v>2060.53</v>
       </c>
-      <c r="V119" s="3" t="n">
+      <c r="X119" s="3" t="n">
         <v>4797.722615555162</v>
       </c>
-      <c r="W119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="3" t="n">
         <v>1127136.8</v>
       </c>
-      <c r="Z119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA119" s="3" t="n">
+      <c r="AB119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC119" s="3" t="n">
         <v>203652.43</v>
       </c>
-      <c r="AB119" s="3" t="n">
+      <c r="AD119" s="3" t="n">
         <v>33697.69</v>
       </c>
-      <c r="AC119" s="3" t="n">
+      <c r="AE119" s="3" t="n">
         <v>1393.41</v>
       </c>
     </row>
@@ -24319,28 +25039,34 @@
         <v>0</v>
       </c>
       <c r="U120" s="2" t="n">
+        <v>251.5060002258354</v>
+      </c>
+      <c r="V120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="2" t="n">
         <v>1758.83</v>
       </c>
-      <c r="V120" s="2" t="inlineStr"/>
-      <c r="W120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X120" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X120" s="2" t="inlineStr"/>
       <c r="Y120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" s="2" t="n">
         <v>1128602.16</v>
       </c>
-      <c r="Z120" s="2" t="n">
+      <c r="AB120" s="2" t="n">
         <v>9467.719999999999</v>
       </c>
-      <c r="AA120" s="2" t="n">
+      <c r="AC120" s="2" t="n">
         <v>142443.73</v>
       </c>
-      <c r="AB120" s="2" t="n">
+      <c r="AD120" s="2" t="n">
         <v>31802.45</v>
       </c>
-      <c r="AC120" s="2" t="n">
+      <c r="AE120" s="2" t="n">
         <v>1399.41</v>
       </c>
     </row>
@@ -24417,33 +25143,39 @@
         <v>40927.83</v>
       </c>
       <c r="T121" s="3" t="n">
+        <v>40722.82498965901</v>
+      </c>
+      <c r="U121" s="3" t="n">
+        <v>205.0070326486505</v>
+      </c>
+      <c r="V121" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="U121" s="3" t="n">
+      <c r="W121" s="3" t="n">
         <v>2622.54</v>
       </c>
-      <c r="V121" s="3" t="n">
+      <c r="X121" s="3" t="n">
         <v>4881.395938124275</v>
       </c>
-      <c r="W121" s="3" t="n">
+      <c r="Y121" s="3" t="n">
         <v>37013.159140806</v>
       </c>
-      <c r="X121" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y121" s="3" t="n">
+      <c r="Z121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="3" t="n">
         <v>1134523.81</v>
       </c>
-      <c r="Z121" s="3" t="n">
+      <c r="AB121" s="3" t="n">
         <v>20892.3</v>
       </c>
-      <c r="AA121" s="3" t="n">
+      <c r="AC121" s="3" t="n">
         <v>170857.05</v>
       </c>
-      <c r="AB121" s="3" t="n">
+      <c r="AD121" s="3" t="n">
         <v>35125.4</v>
       </c>
-      <c r="AC121" s="3" t="n">
+      <c r="AE121" s="3" t="n">
         <v>1405.27</v>
       </c>
     </row>
@@ -24523,28 +25255,34 @@
         <v>0</v>
       </c>
       <c r="U122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="2" t="n">
         <v>1495.71</v>
       </c>
-      <c r="V122" s="2" t="inlineStr"/>
-      <c r="W122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X122" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X122" s="2" t="inlineStr"/>
       <c r="Y122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" s="2" t="n">
         <v>1129366.26</v>
       </c>
-      <c r="Z122" s="2" t="n">
+      <c r="AB122" s="2" t="n">
         <v>19523.26</v>
       </c>
-      <c r="AA122" s="2" t="n">
+      <c r="AC122" s="2" t="n">
         <v>143170.57</v>
       </c>
-      <c r="AB122" s="2" t="n">
+      <c r="AD122" s="2" t="n">
         <v>35467.25</v>
       </c>
-      <c r="AC122" s="2" t="n">
+      <c r="AE122" s="2" t="n">
         <v>1401.53</v>
       </c>
     </row>
@@ -24621,33 +25359,39 @@
         <v>39223.15</v>
       </c>
       <c r="T123" s="3" t="n">
+        <v>39223.15119877394</v>
+      </c>
+      <c r="U123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U123" s="3" t="n">
+      <c r="W123" s="3" t="n">
         <v>2323.32</v>
       </c>
-      <c r="V123" s="3" t="n">
+      <c r="X123" s="3" t="n">
         <v>4537.318933947245</v>
       </c>
-      <c r="W123" s="3" t="n">
+      <c r="Y123" s="3" t="n">
         <v>35877.68758544704</v>
       </c>
-      <c r="X123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y123" s="3" t="n">
+      <c r="Z123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" s="3" t="n">
         <v>1135721.64</v>
       </c>
-      <c r="Z123" s="3" t="n">
+      <c r="AB123" s="3" t="n">
         <v>18952.36</v>
       </c>
-      <c r="AA123" s="3" t="n">
+      <c r="AC123" s="3" t="n">
         <v>184455.23</v>
       </c>
-      <c r="AB123" s="3" t="n">
+      <c r="AD123" s="3" t="n">
         <v>35350.48</v>
       </c>
-      <c r="AC123" s="3" t="n">
+      <c r="AE123" s="3" t="n">
         <v>1406.97</v>
       </c>
     </row>
@@ -24727,28 +25471,34 @@
         <v>0</v>
       </c>
       <c r="U124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" s="2" t="n">
         <v>1287.77</v>
       </c>
-      <c r="V124" s="2" t="inlineStr"/>
-      <c r="W124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X124" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X124" s="2" t="inlineStr"/>
       <c r="Y124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" s="2" t="n">
         <v>1126351.08</v>
       </c>
-      <c r="Z124" s="2" t="n">
+      <c r="AB124" s="2" t="n">
         <v>10637.22</v>
       </c>
-      <c r="AA124" s="2" t="n">
+      <c r="AC124" s="2" t="n">
         <v>150987.56</v>
       </c>
-      <c r="AB124" s="2" t="n">
+      <c r="AD124" s="2" t="n">
         <v>33920.54</v>
       </c>
-      <c r="AC124" s="2" t="n">
+      <c r="AE124" s="2" t="n">
         <v>1394.86</v>
       </c>
     </row>
@@ -24825,33 +25575,39 @@
         <v>40414</v>
       </c>
       <c r="T125" s="3" t="n">
+        <v>40413.99704287824</v>
+      </c>
+      <c r="U125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U125" s="3" t="n">
+      <c r="W125" s="3" t="n">
         <v>2145.76</v>
       </c>
-      <c r="V125" s="3" t="n">
+      <c r="X125" s="3" t="n">
         <v>4807.34209224442</v>
       </c>
-      <c r="W125" s="3" t="n">
+      <c r="Y125" s="3" t="n">
         <v>37413.99704287824</v>
       </c>
-      <c r="X125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y125" s="3" t="n">
+      <c r="Z125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" s="3" t="n">
         <v>1131531.97</v>
       </c>
-      <c r="Z125" s="3" t="n">
+      <c r="AB125" s="3" t="n">
         <v>10354.17</v>
       </c>
-      <c r="AA125" s="3" t="n">
+      <c r="AC125" s="3" t="n">
         <v>196377.16</v>
       </c>
-      <c r="AB125" s="3" t="n">
+      <c r="AD125" s="3" t="n">
         <v>34257.09</v>
       </c>
-      <c r="AC125" s="3" t="n">
+      <c r="AE125" s="3" t="n">
         <v>1400.63</v>
       </c>
     </row>
@@ -24929,28 +25685,34 @@
         <v>0</v>
       </c>
       <c r="U126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V126" s="2" t="inlineStr"/>
-      <c r="W126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X126" s="2" t="inlineStr"/>
       <c r="Y126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="2" t="n">
         <v>1124315.52</v>
       </c>
-      <c r="Z126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA126" s="2" t="n">
+      <c r="AB126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" s="2" t="n">
         <v>158628.74</v>
       </c>
-      <c r="AB126" s="2" t="n">
+      <c r="AD126" s="2" t="n">
         <v>31725.75</v>
       </c>
-      <c r="AC126" s="2" t="n">
+      <c r="AE126" s="2" t="n">
         <v>1388.92</v>
       </c>
     </row>
@@ -25025,33 +25787,39 @@
         <v>40414</v>
       </c>
       <c r="T127" s="3" t="n">
+        <v>40413.99704287824</v>
+      </c>
+      <c r="U127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U127" s="3" t="n">
+      <c r="W127" s="3" t="n">
         <v>2060.53</v>
       </c>
-      <c r="V127" s="3" t="n">
+      <c r="X127" s="3" t="n">
         <v>4797.722615555162</v>
       </c>
-      <c r="W127" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" s="3" t="n">
         <v>1127136.8</v>
       </c>
-      <c r="Z127" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA127" s="3" t="n">
+      <c r="AB127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC127" s="3" t="n">
         <v>203652.43</v>
       </c>
-      <c r="AB127" s="3" t="n">
+      <c r="AD127" s="3" t="n">
         <v>33697.69</v>
       </c>
-      <c r="AC127" s="3" t="n">
+      <c r="AE127" s="3" t="n">
         <v>1393.41</v>
       </c>
     </row>
@@ -25129,28 +25897,34 @@
         <v>0</v>
       </c>
       <c r="U128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V128" s="2" t="inlineStr"/>
-      <c r="W128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X128" s="2" t="inlineStr"/>
       <c r="Y128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" s="2" t="n">
         <v>1124315.52</v>
       </c>
-      <c r="Z128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" s="2" t="n">
+      <c r="AB128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" s="2" t="n">
         <v>158628.74</v>
       </c>
-      <c r="AB128" s="2" t="n">
+      <c r="AD128" s="2" t="n">
         <v>31725.75</v>
       </c>
-      <c r="AC128" s="2" t="n">
+      <c r="AE128" s="2" t="n">
         <v>1388.92</v>
       </c>
     </row>
@@ -25225,33 +25999,39 @@
         <v>40414</v>
       </c>
       <c r="T129" s="3" t="n">
+        <v>40413.99704287824</v>
+      </c>
+      <c r="U129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U129" s="3" t="n">
+      <c r="W129" s="3" t="n">
         <v>2060.53</v>
       </c>
-      <c r="V129" s="3" t="n">
+      <c r="X129" s="3" t="n">
         <v>4797.722615555162</v>
       </c>
-      <c r="W129" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" s="3" t="n">
         <v>1127136.8</v>
       </c>
-      <c r="Z129" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" s="3" t="n">
+      <c r="AB129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" s="3" t="n">
         <v>203652.43</v>
       </c>
-      <c r="AB129" s="3" t="n">
+      <c r="AD129" s="3" t="n">
         <v>33697.69</v>
       </c>
-      <c r="AC129" s="3" t="n">
+      <c r="AE129" s="3" t="n">
         <v>1393.41</v>
       </c>
     </row>
@@ -25329,28 +26109,34 @@
         <v>0</v>
       </c>
       <c r="U130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" s="2" t="n">
         <v>1468.93</v>
       </c>
-      <c r="V130" s="2" t="inlineStr"/>
-      <c r="W130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X130" s="2" t="inlineStr"/>
       <c r="Y130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA130" s="2" t="n">
         <v>1168888.99</v>
       </c>
-      <c r="Z130" s="2" t="n">
+      <c r="AB130" s="2" t="n">
         <v>-2379.9</v>
       </c>
-      <c r="AA130" s="2" t="n">
+      <c r="AC130" s="2" t="n">
         <v>194817.38</v>
       </c>
-      <c r="AB130" s="2" t="n">
+      <c r="AD130" s="2" t="n">
         <v>38487.5</v>
       </c>
-      <c r="AC130" s="2" t="n">
+      <c r="AE130" s="2" t="n">
         <v>1454.33</v>
       </c>
     </row>
@@ -25425,33 +26211,39 @@
         <v>65949.48</v>
       </c>
       <c r="T131" s="3" t="n">
+        <v>65949.48081356927</v>
+      </c>
+      <c r="U131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="U131" s="3" t="n">
+      <c r="W131" s="3" t="n">
         <v>2389.98</v>
       </c>
-      <c r="V131" s="3" t="n">
+      <c r="X131" s="3" t="n">
         <v>11066.11169148027</v>
       </c>
-      <c r="W131" s="3" t="n">
+      <c r="Y131" s="3" t="n">
         <v>54615.99561110905</v>
       </c>
-      <c r="X131" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y131" s="3" t="n">
+      <c r="Z131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA131" s="3" t="n">
         <v>1176071.04</v>
       </c>
-      <c r="Z131" s="3" t="n">
+      <c r="AB131" s="3" t="n">
         <v>-2457.05</v>
       </c>
-      <c r="AA131" s="3" t="n">
+      <c r="AC131" s="3" t="n">
         <v>269428.68</v>
       </c>
-      <c r="AB131" s="3" t="n">
+      <c r="AD131" s="3" t="n">
         <v>45469.66</v>
       </c>
-      <c r="AC131" s="3" t="n">
+      <c r="AE131" s="3" t="n">
         <v>1467.61</v>
       </c>
     </row>
@@ -25529,28 +26321,34 @@
         <v>0</v>
       </c>
       <c r="U132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" s="2" t="n">
         <v>1506.85</v>
       </c>
-      <c r="V132" s="2" t="inlineStr"/>
-      <c r="W132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X132" s="2" t="inlineStr"/>
       <c r="Y132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" s="2" t="n">
         <v>1180714.08</v>
       </c>
-      <c r="Z132" s="2" t="n">
+      <c r="AB132" s="2" t="n">
         <v>-11037.42</v>
       </c>
-      <c r="AA132" s="2" t="n">
+      <c r="AC132" s="2" t="n">
         <v>198601.48</v>
       </c>
-      <c r="AB132" s="2" t="n">
+      <c r="AD132" s="2" t="n">
         <v>37512.81</v>
       </c>
-      <c r="AC132" s="2" t="n">
+      <c r="AE132" s="2" t="n">
         <v>1473.73</v>
       </c>
     </row>
@@ -25625,33 +26423,39 @@
         <v>42420.66</v>
       </c>
       <c r="T133" s="3" t="n">
+        <v>42420.65838754183</v>
+      </c>
+      <c r="U133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U133" s="3" t="n">
+      <c r="W133" s="3" t="n">
         <v>2359.43</v>
       </c>
-      <c r="V133" s="3" t="n">
+      <c r="X133" s="3" t="n">
         <v>10609.67778995354</v>
       </c>
-      <c r="W133" s="3" t="n">
+      <c r="Y133" s="3" t="n">
         <v>39420.65838754183</v>
       </c>
-      <c r="X133" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y133" s="3" t="n">
+      <c r="Z133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="3" t="n">
         <v>1188628.57</v>
       </c>
-      <c r="Z133" s="3" t="n">
+      <c r="AB133" s="3" t="n">
         <v>-10918.46</v>
       </c>
-      <c r="AA133" s="3" t="n">
+      <c r="AC133" s="3" t="n">
         <v>252105.57</v>
       </c>
-      <c r="AB133" s="3" t="n">
+      <c r="AD133" s="3" t="n">
         <v>48237.42</v>
       </c>
-      <c r="AC133" s="3" t="n">
+      <c r="AE133" s="3" t="n">
         <v>1486.47</v>
       </c>
     </row>
@@ -25729,28 +26533,34 @@
         <v>0</v>
       </c>
       <c r="U134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V134" s="2" t="inlineStr"/>
-      <c r="W134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X134" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X134" s="2" t="inlineStr"/>
       <c r="Y134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" s="2" t="n">
         <v>1191301.43</v>
       </c>
-      <c r="Z134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA134" s="2" t="n">
+      <c r="AB134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" s="2" t="n">
         <v>242486.92</v>
       </c>
-      <c r="AB134" s="2" t="n">
+      <c r="AD134" s="2" t="n">
         <v>48497.38</v>
       </c>
-      <c r="AC134" s="2" t="n">
+      <c r="AE134" s="2" t="n">
         <v>1489.55</v>
       </c>
     </row>
@@ -25825,33 +26635,39 @@
         <v>42420.66</v>
       </c>
       <c r="T135" s="3" t="n">
+        <v>42420.65838754183</v>
+      </c>
+      <c r="U135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U135" s="3" t="n">
+      <c r="W135" s="3" t="n">
         <v>2055.72</v>
       </c>
-      <c r="V135" s="3" t="n">
+      <c r="X135" s="3" t="n">
         <v>10458.50309561752</v>
       </c>
-      <c r="W135" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" s="3" t="n">
         <v>1198645.51</v>
       </c>
-      <c r="Z135" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA135" s="3" t="n">
+      <c r="AB135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" s="3" t="n">
         <v>295173.25</v>
       </c>
-      <c r="AB135" s="3" t="n">
+      <c r="AD135" s="3" t="n">
         <v>51600.52</v>
       </c>
-      <c r="AC135" s="3" t="n">
+      <c r="AE135" s="3" t="n">
         <v>1500.84</v>
       </c>
     </row>
@@ -25931,28 +26747,34 @@
         <v>0</v>
       </c>
       <c r="U136" s="2" t="n">
+        <v>1756.091491718071</v>
+      </c>
+      <c r="V136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" s="2" t="n">
         <v>1823.87</v>
       </c>
-      <c r="V136" s="2" t="inlineStr"/>
-      <c r="W136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X136" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X136" s="2" t="inlineStr"/>
       <c r="Y136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="2" t="n">
         <v>1162408.88</v>
       </c>
-      <c r="Z136" s="2" t="n">
+      <c r="AB136" s="2" t="n">
         <v>1864.86</v>
       </c>
-      <c r="AA136" s="2" t="n">
+      <c r="AC136" s="2" t="n">
         <v>164318.46</v>
       </c>
-      <c r="AB136" s="2" t="n">
+      <c r="AD136" s="2" t="n">
         <v>33419.48</v>
       </c>
-      <c r="AC136" s="2" t="n">
+      <c r="AE136" s="2" t="n">
         <v>1445.08</v>
       </c>
     </row>
@@ -26029,33 +26851,39 @@
         <v>45278.45</v>
       </c>
       <c r="T137" s="3" t="n">
+        <v>43582.50261992461</v>
+      </c>
+      <c r="U137" s="3" t="n">
+        <v>1695.945460149653</v>
+      </c>
+      <c r="V137" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="U137" s="3" t="n">
+      <c r="W137" s="3" t="n">
         <v>2702.3</v>
       </c>
-      <c r="V137" s="3" t="n">
+      <c r="X137" s="3" t="n">
         <v>5435.441971458262</v>
       </c>
-      <c r="W137" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA137" s="3" t="n">
         <v>1166588.47</v>
       </c>
-      <c r="Z137" s="3" t="n">
+      <c r="AB137" s="3" t="n">
         <v>-5699.05</v>
       </c>
-      <c r="AA137" s="3" t="n">
+      <c r="AC137" s="3" t="n">
         <v>221146.66</v>
       </c>
-      <c r="AB137" s="3" t="n">
+      <c r="AD137" s="3" t="n">
         <v>41818.12</v>
       </c>
-      <c r="AC137" s="3" t="n">
+      <c r="AE137" s="3" t="n">
         <v>1434.73</v>
       </c>
     </row>
@@ -26135,28 +26963,34 @@
         <v>0</v>
       </c>
       <c r="U138" s="2" t="n">
+        <v>1061.863062175814</v>
+      </c>
+      <c r="V138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" s="2" t="n">
         <v>1557.67</v>
       </c>
-      <c r="V138" s="2" t="inlineStr"/>
-      <c r="W138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X138" s="2" t="inlineStr"/>
       <c r="Y138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA138" s="2" t="n">
         <v>1164723.49</v>
       </c>
-      <c r="Z138" s="2" t="n">
+      <c r="AB138" s="2" t="n">
         <v>-1286.46</v>
       </c>
-      <c r="AA138" s="2" t="n">
+      <c r="AC138" s="2" t="n">
         <v>186662.58</v>
       </c>
-      <c r="AB138" s="2" t="n">
+      <c r="AD138" s="2" t="n">
         <v>37075.22</v>
       </c>
-      <c r="AC138" s="2" t="n">
+      <c r="AE138" s="2" t="n">
         <v>1448.44</v>
       </c>
     </row>
@@ -26233,33 +27067,39 @@
         <v>45928.96</v>
       </c>
       <c r="T139" s="3" t="n">
+        <v>45556.98697823905</v>
+      </c>
+      <c r="U139" s="3" t="n">
+        <v>371.9713593522429</v>
+      </c>
+      <c r="V139" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="U139" s="3" t="n">
+      <c r="W139" s="3" t="n">
         <v>2449.94</v>
       </c>
-      <c r="V139" s="3" t="n">
+      <c r="X139" s="3" t="n">
         <v>13916.99919482041</v>
       </c>
-      <c r="W139" s="3" t="n">
+      <c r="Y139" s="3" t="n">
         <v>35968.31888822916</v>
       </c>
-      <c r="X139" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y139" s="3" t="n">
+      <c r="Z139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="3" t="n">
         <v>1174413.48</v>
       </c>
-      <c r="Z139" s="3" t="n">
+      <c r="AB139" s="3" t="n">
         <v>-1401.18</v>
       </c>
-      <c r="AA139" s="3" t="n">
+      <c r="AC139" s="3" t="n">
         <v>244059.79</v>
       </c>
-      <c r="AB139" s="3" t="n">
+      <c r="AD139" s="3" t="n">
         <v>45069.64</v>
       </c>
-      <c r="AC139" s="3" t="n">
+      <c r="AE139" s="3" t="n">
         <v>1465.14</v>
       </c>
     </row>
@@ -26339,28 +27179,34 @@
         <v>0</v>
       </c>
       <c r="U140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" s="2" t="n">
         <v>1329.67</v>
       </c>
-      <c r="V140" s="2" t="inlineStr"/>
-      <c r="W140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X140" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X140" s="2" t="inlineStr"/>
       <c r="Y140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" s="2" t="n">
         <v>1175132.96</v>
       </c>
-      <c r="Z140" s="2" t="n">
+      <c r="AB140" s="2" t="n">
         <v>-6093.9</v>
       </c>
-      <c r="AA140" s="2" t="n">
+      <c r="AC140" s="2" t="n">
         <v>218766.67</v>
       </c>
-      <c r="AB140" s="2" t="n">
+      <c r="AD140" s="2" t="n">
         <v>41620.47</v>
       </c>
-      <c r="AC140" s="2" t="n">
+      <c r="AE140" s="2" t="n">
         <v>1466.31</v>
       </c>
     </row>
@@ -26437,33 +27283,39 @@
         <v>48314.49</v>
       </c>
       <c r="T141" s="3" t="n">
+        <v>48314.49340473423</v>
+      </c>
+      <c r="U141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="U141" s="3" t="n">
+      <c r="W141" s="3" t="n">
         <v>2318.18</v>
       </c>
-      <c r="V141" s="3" t="n">
+      <c r="X141" s="3" t="n">
         <v>10219.63770568068</v>
       </c>
-      <c r="W141" s="3" t="n">
+      <c r="Y141" s="3" t="n">
         <v>39420.65838754183</v>
       </c>
-      <c r="X141" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y141" s="3" t="n">
+      <c r="Z141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="3" t="n">
         <v>1183381.54</v>
       </c>
-      <c r="Z141" s="3" t="n">
+      <c r="AB141" s="3" t="n">
         <v>261.84</v>
       </c>
-      <c r="AA141" s="3" t="n">
+      <c r="AC141" s="3" t="n">
         <v>270510.05</v>
       </c>
-      <c r="AB141" s="3" t="n">
+      <c r="AD141" s="3" t="n">
         <v>47282.07</v>
       </c>
-      <c r="AC141" s="3" t="n">
+      <c r="AE141" s="3" t="n">
         <v>1478.57</v>
       </c>
     </row>
@@ -26541,28 +27393,34 @@
         <v>0</v>
       </c>
       <c r="U142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" s="2" t="n">
         <v>1444.07</v>
       </c>
-      <c r="V142" s="2" t="inlineStr"/>
-      <c r="W142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X142" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X142" s="2" t="inlineStr"/>
       <c r="Y142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="2" t="n">
         <v>1176999.18</v>
       </c>
-      <c r="Z142" s="2" t="n">
+      <c r="AB142" s="2" t="n">
         <v>-4528.28</v>
       </c>
-      <c r="AA142" s="2" t="n">
+      <c r="AC142" s="2" t="n">
         <v>203324.94</v>
       </c>
-      <c r="AB142" s="2" t="n">
+      <c r="AD142" s="2" t="n">
         <v>39759.33</v>
       </c>
-      <c r="AC142" s="2" t="n">
+      <c r="AE142" s="2" t="n">
         <v>1468.13</v>
       </c>
     </row>
@@ -26637,33 +27495,39 @@
         <v>42420.66</v>
       </c>
       <c r="T143" s="3" t="n">
+        <v>42420.65838754183</v>
+      </c>
+      <c r="U143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U143" s="3" t="n">
+      <c r="W143" s="3" t="n">
         <v>2298.2</v>
       </c>
-      <c r="V143" s="3" t="n">
+      <c r="X143" s="3" t="n">
         <v>10719.94477155944</v>
       </c>
-      <c r="W143" s="3" t="n">
+      <c r="Y143" s="3" t="n">
         <v>39420.65838754183</v>
       </c>
-      <c r="X143" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y143" s="3" t="n">
+      <c r="Z143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA143" s="3" t="n">
         <v>1185001.45</v>
       </c>
-      <c r="Z143" s="3" t="n">
+      <c r="AB143" s="3" t="n">
         <v>-4495.6</v>
       </c>
-      <c r="AA143" s="3" t="n">
+      <c r="AC143" s="3" t="n">
         <v>256679.54</v>
       </c>
-      <c r="AB143" s="3" t="n">
+      <c r="AD143" s="3" t="n">
         <v>47682.66</v>
       </c>
-      <c r="AC143" s="3" t="n">
+      <c r="AE143" s="3" t="n">
         <v>1481</v>
       </c>
     </row>
@@ -26741,28 +27605,34 @@
         <v>0</v>
       </c>
       <c r="U144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V144" s="2" t="inlineStr"/>
-      <c r="W144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X144" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X144" s="2" t="inlineStr"/>
       <c r="Y144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA144" s="2" t="n">
         <v>1191301.43</v>
       </c>
-      <c r="Z144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA144" s="2" t="n">
+      <c r="AB144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" s="2" t="n">
         <v>242486.92</v>
       </c>
-      <c r="AB144" s="2" t="n">
+      <c r="AD144" s="2" t="n">
         <v>48497.38</v>
       </c>
-      <c r="AC144" s="2" t="n">
+      <c r="AE144" s="2" t="n">
         <v>1489.55</v>
       </c>
     </row>
@@ -26837,33 +27707,39 @@
         <v>42420.66</v>
       </c>
       <c r="T145" s="3" t="n">
+        <v>42420.65838754183</v>
+      </c>
+      <c r="U145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U145" s="3" t="n">
+      <c r="W145" s="3" t="n">
         <v>2055.72</v>
       </c>
-      <c r="V145" s="3" t="n">
+      <c r="X145" s="3" t="n">
         <v>10458.50309561752</v>
       </c>
-      <c r="W145" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X145" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="3" t="n">
         <v>1198645.51</v>
       </c>
-      <c r="Z145" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA145" s="3" t="n">
+      <c r="AB145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" s="3" t="n">
         <v>295173.25</v>
       </c>
-      <c r="AB145" s="3" t="n">
+      <c r="AD145" s="3" t="n">
         <v>51600.52</v>
       </c>
-      <c r="AC145" s="3" t="n">
+      <c r="AE145" s="3" t="n">
         <v>1500.84</v>
       </c>
     </row>
@@ -26941,28 +27817,34 @@
         <v>0</v>
       </c>
       <c r="U146" s="2" t="n">
+        <v>4116.586735691439</v>
+      </c>
+      <c r="V146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W146" s="2" t="n">
         <v>1400.47</v>
       </c>
-      <c r="V146" s="2" t="inlineStr"/>
-      <c r="W146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X146" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X146" s="2" t="inlineStr"/>
       <c r="Y146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="2" t="n">
         <v>827126.97</v>
       </c>
-      <c r="Z146" s="2" t="n">
+      <c r="AB146" s="2" t="n">
         <v>1269</v>
       </c>
-      <c r="AA146" s="2" t="n">
+      <c r="AC146" s="2" t="n">
         <v>-168769.69</v>
       </c>
-      <c r="AB146" s="2" t="n">
+      <c r="AD146" s="2" t="n">
         <v>129.1</v>
       </c>
-      <c r="AC146" s="2" t="n">
+      <c r="AE146" s="2" t="n">
         <v>992.64</v>
       </c>
     </row>
@@ -27037,33 +27919,39 @@
         <v>215571.46</v>
       </c>
       <c r="T147" s="3" t="n">
+        <v>153236.9756145912</v>
+      </c>
+      <c r="U147" s="3" t="n">
+        <v>62334.48763033</v>
+      </c>
+      <c r="V147" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="U147" s="3" t="n">
+      <c r="W147" s="3" t="n">
         <v>4169.32</v>
       </c>
-      <c r="V147" s="3" t="n">
+      <c r="X147" s="3" t="n">
         <v>-11924.79818977951</v>
       </c>
-      <c r="W147" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X147" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA147" s="3" t="n">
         <v>815345.59</v>
       </c>
-      <c r="Z147" s="3" t="n">
+      <c r="AB147" s="3" t="n">
         <v>63672.19</v>
       </c>
-      <c r="AA147" s="3" t="n">
+      <c r="AC147" s="3" t="n">
         <v>-29285.08</v>
       </c>
-      <c r="AB147" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC147" s="3" t="n">
+      <c r="AD147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE147" s="3" t="n">
         <v>978.33</v>
       </c>
     </row>
@@ -27141,28 +28029,34 @@
         <v>0</v>
       </c>
       <c r="U148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V148" s="2" t="inlineStr"/>
-      <c r="W148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X148" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X148" s="2" t="inlineStr"/>
       <c r="Y148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="2" t="n">
         <v>834599.05</v>
       </c>
-      <c r="Z148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA148" s="2" t="n">
+      <c r="AB148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC148" s="2" t="n">
         <v>-164250.93</v>
       </c>
-      <c r="AB148" s="2" t="n">
+      <c r="AD148" s="2" t="n">
         <v>-1050</v>
       </c>
-      <c r="AC148" s="2" t="n">
+      <c r="AE148" s="2" t="n">
         <v>1001.46</v>
       </c>
     </row>
@@ -27237,33 +28131,39 @@
         <v>212394.84</v>
       </c>
       <c r="T149" s="3" t="n">
+        <v>212394.8370908322</v>
+      </c>
+      <c r="U149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="U149" s="3" t="n">
+      <c r="W149" s="3" t="n">
         <v>3977.99</v>
       </c>
-      <c r="V149" s="3" t="n">
+      <c r="X149" s="3" t="n">
         <v>-18750.56534802529</v>
       </c>
-      <c r="W149" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X149" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="3" t="n">
         <v>815870.99</v>
       </c>
-      <c r="Z149" s="3" t="n">
+      <c r="AB149" s="3" t="n">
         <v>57903.12</v>
       </c>
-      <c r="AA149" s="3" t="n">
+      <c r="AC149" s="3" t="n">
         <v>-25730.35</v>
       </c>
-      <c r="AB149" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC149" s="3" t="n">
+      <c r="AD149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE149" s="3" t="n">
         <v>978.96</v>
       </c>
     </row>
@@ -27341,28 +28241,34 @@
         <v>0</v>
       </c>
       <c r="U150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V150" s="2" t="inlineStr"/>
-      <c r="W150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X150" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X150" s="2" t="inlineStr"/>
       <c r="Y150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA150" s="2" t="n">
         <v>834599.05</v>
       </c>
-      <c r="Z150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA150" s="2" t="n">
+      <c r="AB150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" s="2" t="n">
         <v>-164250.93</v>
       </c>
-      <c r="AB150" s="2" t="n">
+      <c r="AD150" s="2" t="n">
         <v>-1050</v>
       </c>
-      <c r="AC150" s="2" t="n">
+      <c r="AE150" s="2" t="n">
         <v>1001.46</v>
       </c>
     </row>
@@ -27437,33 +28343,39 @@
         <v>212394.84</v>
       </c>
       <c r="T151" s="3" t="n">
+        <v>212394.8370908322</v>
+      </c>
+      <c r="U151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="U151" s="3" t="n">
+      <c r="W151" s="3" t="n">
         <v>3977.99</v>
       </c>
-      <c r="V151" s="3" t="n">
+      <c r="X151" s="3" t="n">
         <v>-18750.56534802529</v>
       </c>
-      <c r="W151" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X151" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="3" t="n">
         <v>815870.99</v>
       </c>
-      <c r="Z151" s="3" t="n">
+      <c r="AB151" s="3" t="n">
         <v>57903.12</v>
       </c>
-      <c r="AA151" s="3" t="n">
+      <c r="AC151" s="3" t="n">
         <v>-25730.35</v>
       </c>
-      <c r="AB151" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC151" s="3" t="n">
+      <c r="AD151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE151" s="3" t="n">
         <v>978.96</v>
       </c>
     </row>
@@ -27543,28 +28455,34 @@
         <v>0</v>
       </c>
       <c r="U152" s="2" t="n">
+        <v>8569.977142676089</v>
+      </c>
+      <c r="V152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" s="2" t="n">
         <v>1632.1</v>
       </c>
-      <c r="V152" s="2" t="inlineStr"/>
-      <c r="W152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X152" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X152" s="2" t="inlineStr"/>
       <c r="Y152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA152" s="2" t="n">
         <v>815443.48</v>
       </c>
-      <c r="Z152" s="2" t="n">
+      <c r="AB152" s="2" t="n">
         <v>-20681.27</v>
       </c>
-      <c r="AA152" s="2" t="n">
+      <c r="AC152" s="2" t="n">
         <v>-156129.16</v>
       </c>
-      <c r="AB152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC152" s="2" t="n">
+      <c r="AD152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" s="2" t="n">
         <v>978.45</v>
       </c>
     </row>
@@ -27641,33 +28559,39 @@
         <v>179780.35</v>
       </c>
       <c r="T153" s="3" t="n">
+        <v>159687.4475114033</v>
+      </c>
+      <c r="U153" s="3" t="n">
+        <v>20092.90419164136</v>
+      </c>
+      <c r="V153" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="U153" s="3" t="n">
+      <c r="W153" s="3" t="n">
         <v>5358.08</v>
       </c>
-      <c r="V153" s="3" t="n">
+      <c r="X153" s="3" t="n">
         <v>-11923.6653725768</v>
       </c>
-      <c r="W153" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X153" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA153" s="3" t="n">
         <v>803534.12</v>
       </c>
-      <c r="Z153" s="3" t="n">
+      <c r="AB153" s="3" t="n">
         <v>7919.67</v>
       </c>
-      <c r="AA153" s="3" t="n">
+      <c r="AC153" s="3" t="n">
         <v>-28817.82</v>
       </c>
-      <c r="AB153" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC153" s="3" t="n">
+      <c r="AD153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE153" s="3" t="n">
         <v>964.14</v>
       </c>
     </row>
@@ -27747,28 +28671,34 @@
         <v>0</v>
       </c>
       <c r="U154" s="2" t="n">
+        <v>1038.285539515466</v>
+      </c>
+      <c r="V154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W154" s="2" t="n">
         <v>1338.85</v>
       </c>
-      <c r="V154" s="2" t="inlineStr"/>
-      <c r="W154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X154" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X154" s="2" t="inlineStr"/>
       <c r="Y154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA154" s="2" t="n">
         <v>816676.61</v>
       </c>
-      <c r="Z154" s="2" t="n">
+      <c r="AB154" s="2" t="n">
         <v>-15998.35</v>
       </c>
-      <c r="AA154" s="2" t="n">
+      <c r="AC154" s="2" t="n">
         <v>-165717.09</v>
       </c>
-      <c r="AB154" s="2" t="n">
+      <c r="AD154" s="2" t="n">
         <v>-931.29</v>
       </c>
-      <c r="AC154" s="2" t="n">
+      <c r="AE154" s="2" t="n">
         <v>979.9299999999999</v>
       </c>
     </row>
@@ -27845,33 +28775,39 @@
         <v>224326.74</v>
       </c>
       <c r="T155" s="3" t="n">
+        <v>205602.776601632</v>
+      </c>
+      <c r="U155" s="3" t="n">
+        <v>18723.96379386214</v>
+      </c>
+      <c r="V155" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="U155" s="3" t="n">
+      <c r="W155" s="3" t="n">
         <v>5051.66</v>
       </c>
-      <c r="V155" s="3" t="n">
+      <c r="X155" s="3" t="n">
         <v>-17578.78449015121</v>
       </c>
-      <c r="W155" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X155" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" s="3" t="n">
         <v>799118.92</v>
       </c>
-      <c r="Z155" s="3" t="n">
+      <c r="AB155" s="3" t="n">
         <v>46587.08</v>
       </c>
-      <c r="AA155" s="3" t="n">
+      <c r="AC155" s="3" t="n">
         <v>-28124.69</v>
       </c>
-      <c r="AB155" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC155" s="3" t="n">
+      <c r="AD155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE155" s="3" t="n">
         <v>958.83</v>
       </c>
     </row>
@@ -27951,28 +28887,34 @@
         <v>0</v>
       </c>
       <c r="U156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" s="2" t="n">
         <v>1209.58</v>
       </c>
-      <c r="V156" s="2" t="inlineStr"/>
-      <c r="W156" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X156" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X156" s="2" t="inlineStr"/>
       <c r="Y156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA156" s="2" t="n">
         <v>832354</v>
       </c>
-      <c r="Z156" s="2" t="n">
+      <c r="AB156" s="2" t="n">
         <v>-1878.59</v>
       </c>
-      <c r="AA156" s="2" t="n">
+      <c r="AC156" s="2" t="n">
         <v>-164278.23</v>
       </c>
-      <c r="AB156" s="2" t="n">
+      <c r="AD156" s="2" t="n">
         <v>-657.51</v>
       </c>
-      <c r="AC156" s="2" t="n">
+      <c r="AE156" s="2" t="n">
         <v>999.28</v>
       </c>
     </row>
@@ -28049,33 +28991,39 @@
         <v>211759.44</v>
       </c>
       <c r="T157" s="3" t="n">
+        <v>211759.4405057414</v>
+      </c>
+      <c r="U157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="U157" s="3" t="n">
+      <c r="W157" s="3" t="n">
         <v>4396.32</v>
       </c>
-      <c r="V157" s="3" t="n">
+      <c r="X157" s="3" t="n">
         <v>-17998.44410972577</v>
       </c>
-      <c r="W157" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X157" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="3" t="n">
         <v>814803.13</v>
       </c>
-      <c r="Z157" s="3" t="n">
+      <c r="AB157" s="3" t="n">
         <v>56725.06</v>
       </c>
-      <c r="AA157" s="3" t="n">
+      <c r="AC157" s="3" t="n">
         <v>-25934.15</v>
       </c>
-      <c r="AB157" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC157" s="3" t="n">
+      <c r="AD157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="3" t="n">
         <v>977.6799999999999</v>
       </c>
     </row>
@@ -28153,28 +29101,34 @@
         <v>0</v>
       </c>
       <c r="U158" s="2" t="n">
+        <v>3488.362120695312</v>
+      </c>
+      <c r="V158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W158" s="2" t="n">
         <v>1464.13</v>
       </c>
-      <c r="V158" s="2" t="inlineStr"/>
-      <c r="W158" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X158" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X158" s="2" t="inlineStr"/>
       <c r="Y158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="2" t="n">
         <v>817544.45</v>
       </c>
-      <c r="Z158" s="2" t="n">
+      <c r="AB158" s="2" t="n">
         <v>-10220.16</v>
       </c>
-      <c r="AA158" s="2" t="n">
+      <c r="AC158" s="2" t="n">
         <v>-169201.51</v>
       </c>
-      <c r="AB158" s="2" t="n">
+      <c r="AD158" s="2" t="n">
         <v>-476.43</v>
       </c>
-      <c r="AC158" s="2" t="n">
+      <c r="AE158" s="2" t="n">
         <v>980.97</v>
       </c>
     </row>
@@ -28249,33 +29203,39 @@
         <v>203894.56</v>
       </c>
       <c r="T159" s="3" t="n">
+        <v>197769.6410566653</v>
+      </c>
+      <c r="U159" s="3" t="n">
+        <v>6124.923732816975</v>
+      </c>
+      <c r="V159" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="U159" s="3" t="n">
+      <c r="W159" s="3" t="n">
         <v>5395.22</v>
       </c>
-      <c r="V159" s="3" t="n">
+      <c r="X159" s="3" t="n">
         <v>-17898.98735740362</v>
       </c>
-      <c r="W159" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X159" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA159" s="3" t="n">
         <v>799666.9399999999</v>
       </c>
-      <c r="Z159" s="3" t="n">
+      <c r="AB159" s="3" t="n">
         <v>36496.29</v>
       </c>
-      <c r="AA159" s="3" t="n">
+      <c r="AC159" s="3" t="n">
         <v>-29838.71</v>
       </c>
-      <c r="AB159" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC159" s="3" t="n">
+      <c r="AD159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE159" s="3" t="n">
         <v>959.49</v>
       </c>
     </row>
@@ -28353,28 +29313,34 @@
         <v>0</v>
       </c>
       <c r="U160" s="2" t="n">
+        <v>2915.052469981312</v>
+      </c>
+      <c r="V160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W160" s="2" t="n">
         <v>1418.75</v>
       </c>
-      <c r="V160" s="2" t="inlineStr"/>
-      <c r="W160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X160" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X160" s="2" t="inlineStr"/>
       <c r="Y160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA160" s="2" t="n">
         <v>831444.4300000001</v>
       </c>
-      <c r="Z160" s="2" t="n">
+      <c r="AB160" s="2" t="n">
         <v>4255.11</v>
       </c>
-      <c r="AA160" s="2" t="n">
+      <c r="AC160" s="2" t="n">
         <v>-168909.99</v>
       </c>
-      <c r="AB160" s="2" t="n">
+      <c r="AD160" s="2" t="n">
         <v>-163.01</v>
       </c>
-      <c r="AC160" s="2" t="n">
+      <c r="AE160" s="2" t="n">
         <v>997.67</v>
       </c>
     </row>
@@ -28449,33 +29415,39 @@
         <v>194355.54</v>
       </c>
       <c r="T161" s="3" t="n">
+        <v>191040.6774008514</v>
+      </c>
+      <c r="U161" s="3" t="n">
+        <v>3314.867381088627</v>
+      </c>
+      <c r="V161" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="U161" s="3" t="n">
+      <c r="W161" s="3" t="n">
         <v>4232.52</v>
       </c>
-      <c r="V161" s="3" t="n">
+      <c r="X161" s="3" t="n">
         <v>-18068.9141698305</v>
       </c>
-      <c r="W161" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X161" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA161" s="3" t="n">
         <v>813397.1899999999</v>
       </c>
-      <c r="Z161" s="3" t="n">
+      <c r="AB161" s="3" t="n">
         <v>39895.79</v>
       </c>
-      <c r="AA161" s="3" t="n">
+      <c r="AC161" s="3" t="n">
         <v>-29458.41</v>
       </c>
-      <c r="AB161" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC161" s="3" t="n">
+      <c r="AD161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE161" s="3" t="n">
         <v>975.99</v>
       </c>
     </row>
@@ -28553,28 +29525,34 @@
         <v>0</v>
       </c>
       <c r="U162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V162" s="2" t="inlineStr"/>
-      <c r="W162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X162" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X162" s="2" t="inlineStr"/>
       <c r="Y162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="2" t="n">
         <v>1068699.1</v>
       </c>
-      <c r="Z162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA162" s="2" t="n">
+      <c r="AB162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" s="2" t="n">
         <v>89003.78</v>
       </c>
-      <c r="AB162" s="2" t="n">
+      <c r="AD162" s="2" t="n">
         <v>17800.76</v>
       </c>
-      <c r="AC162" s="2" t="n">
+      <c r="AE162" s="2" t="n">
         <v>1305.37</v>
       </c>
     </row>
@@ -28649,33 +29627,39 @@
         <v>43712.25</v>
       </c>
       <c r="T163" s="3" t="n">
+        <v>43712.25322739236</v>
+      </c>
+      <c r="U163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="U163" s="3" t="n">
+      <c r="W163" s="3" t="n">
         <v>2092.18</v>
       </c>
-      <c r="V163" s="3" t="n">
+      <c r="X163" s="3" t="n">
         <v>-1214.132802264299</v>
       </c>
-      <c r="W163" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X163" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA163" s="3" t="n">
         <v>1066710.52</v>
       </c>
-      <c r="Z163" s="3" t="n">
+      <c r="AB163" s="3" t="n">
         <v>251.06</v>
       </c>
-      <c r="AA163" s="3" t="n">
+      <c r="AC163" s="3" t="n">
         <v>131094.45</v>
       </c>
-      <c r="AB163" s="3" t="n">
+      <c r="AD163" s="3" t="n">
         <v>18576.65</v>
       </c>
-      <c r="AC163" s="3" t="n">
+      <c r="AE163" s="3" t="n">
         <v>1303.91</v>
       </c>
     </row>
@@ -28753,28 +29737,34 @@
         <v>0</v>
       </c>
       <c r="U164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V164" s="2" t="inlineStr"/>
-      <c r="W164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X164" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X164" s="2" t="inlineStr"/>
       <c r="Y164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA164" s="2" t="n">
         <v>1068699.1</v>
       </c>
-      <c r="Z164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA164" s="2" t="n">
+      <c r="AB164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC164" s="2" t="n">
         <v>89003.78</v>
       </c>
-      <c r="AB164" s="2" t="n">
+      <c r="AD164" s="2" t="n">
         <v>17800.76</v>
       </c>
-      <c r="AC164" s="2" t="n">
+      <c r="AE164" s="2" t="n">
         <v>1305.37</v>
       </c>
     </row>
@@ -28849,33 +29839,39 @@
         <v>43712.25</v>
       </c>
       <c r="T165" s="3" t="n">
+        <v>43712.25322739236</v>
+      </c>
+      <c r="U165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V165" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="U165" s="3" t="n">
+      <c r="W165" s="3" t="n">
         <v>2092.18</v>
       </c>
-      <c r="V165" s="3" t="n">
+      <c r="X165" s="3" t="n">
         <v>-1214.132802264299</v>
       </c>
-      <c r="W165" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X165" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="3" t="n">
         <v>1066710.52</v>
       </c>
-      <c r="Z165" s="3" t="n">
+      <c r="AB165" s="3" t="n">
         <v>251.06</v>
       </c>
-      <c r="AA165" s="3" t="n">
+      <c r="AC165" s="3" t="n">
         <v>131094.45</v>
       </c>
-      <c r="AB165" s="3" t="n">
+      <c r="AD165" s="3" t="n">
         <v>18576.65</v>
       </c>
-      <c r="AC165" s="3" t="n">
+      <c r="AE165" s="3" t="n">
         <v>1303.91</v>
       </c>
     </row>
@@ -28953,28 +29949,34 @@
         <v>0</v>
       </c>
       <c r="U166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V166" s="2" t="inlineStr"/>
-      <c r="W166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X166" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X166" s="2" t="inlineStr"/>
       <c r="Y166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA166" s="2" t="n">
         <v>1068699.1</v>
       </c>
-      <c r="Z166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA166" s="2" t="n">
+      <c r="AB166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" s="2" t="n">
         <v>89003.78</v>
       </c>
-      <c r="AB166" s="2" t="n">
+      <c r="AD166" s="2" t="n">
         <v>17800.76</v>
       </c>
-      <c r="AC166" s="2" t="n">
+      <c r="AE166" s="2" t="n">
         <v>1305.37</v>
       </c>
     </row>
@@ -29049,33 +30051,39 @@
         <v>43712.25</v>
       </c>
       <c r="T167" s="3" t="n">
+        <v>43712.25322739236</v>
+      </c>
+      <c r="U167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="U167" s="3" t="n">
+      <c r="W167" s="3" t="n">
         <v>2092.18</v>
       </c>
-      <c r="V167" s="3" t="n">
+      <c r="X167" s="3" t="n">
         <v>-1214.132802264299</v>
       </c>
-      <c r="W167" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X167" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA167" s="3" t="n">
         <v>1066710.52</v>
       </c>
-      <c r="Z167" s="3" t="n">
+      <c r="AB167" s="3" t="n">
         <v>251.06</v>
       </c>
-      <c r="AA167" s="3" t="n">
+      <c r="AC167" s="3" t="n">
         <v>131094.45</v>
       </c>
-      <c r="AB167" s="3" t="n">
+      <c r="AD167" s="3" t="n">
         <v>18576.65</v>
       </c>
-      <c r="AC167" s="3" t="n">
+      <c r="AE167" s="3" t="n">
         <v>1303.91</v>
       </c>
     </row>
@@ -29155,28 +30163,34 @@
         <v>0</v>
       </c>
       <c r="U168" s="2" t="n">
+        <v>2008.534311748293</v>
+      </c>
+      <c r="V168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W168" s="2" t="n">
         <v>1616.94</v>
       </c>
-      <c r="V168" s="2" t="inlineStr"/>
-      <c r="W168" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X168" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X168" s="2" t="inlineStr"/>
       <c r="Y168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA168" s="2" t="n">
         <v>1069561.52</v>
       </c>
-      <c r="Z168" s="2" t="n">
+      <c r="AB168" s="2" t="n">
         <v>13361.32</v>
       </c>
-      <c r="AA168" s="2" t="n">
+      <c r="AC168" s="2" t="n">
         <v>77478.25999999999</v>
       </c>
-      <c r="AB168" s="2" t="n">
+      <c r="AD168" s="2" t="n">
         <v>20172.11</v>
       </c>
-      <c r="AC168" s="2" t="n">
+      <c r="AE168" s="2" t="n">
         <v>1310.78</v>
       </c>
     </row>
@@ -29253,33 +30267,39 @@
         <v>37164.57</v>
       </c>
       <c r="T169" s="3" t="n">
+        <v>35970.30105161355</v>
+      </c>
+      <c r="U169" s="3" t="n">
+        <v>1194.267586142875</v>
+      </c>
+      <c r="V169" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="U169" s="3" t="n">
+      <c r="W169" s="3" t="n">
         <v>2532.27</v>
       </c>
-      <c r="V169" s="3" t="n">
+      <c r="X169" s="3" t="n">
         <v>-13391.13750698464</v>
       </c>
-      <c r="W169" s="3" t="n">
+      <c r="Y169" s="3" t="n">
         <v>28458.23046635011</v>
       </c>
-      <c r="X169" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y169" s="3" t="n">
+      <c r="Z169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA169" s="3" t="n">
         <v>1060244.23</v>
       </c>
-      <c r="Z169" s="3" t="n">
+      <c r="AB169" s="3" t="n">
         <v>22556.41</v>
       </c>
-      <c r="AA169" s="3" t="n">
+      <c r="AC169" s="3" t="n">
         <v>83475.77</v>
       </c>
-      <c r="AB169" s="3" t="n">
+      <c r="AD169" s="3" t="n">
         <v>18452.2</v>
       </c>
-      <c r="AC169" s="3" t="n">
+      <c r="AE169" s="3" t="n">
         <v>1281.53</v>
       </c>
     </row>
@@ -29359,28 +30379,34 @@
         <v>0</v>
       </c>
       <c r="U170" s="2" t="n">
+        <v>164.0452409987395</v>
+      </c>
+      <c r="V170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" s="2" t="n">
         <v>1419.94</v>
       </c>
-      <c r="V170" s="2" t="inlineStr"/>
-      <c r="W170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X170" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X170" s="2" t="inlineStr"/>
       <c r="Y170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA170" s="2" t="n">
         <v>1071817.93</v>
       </c>
-      <c r="Z170" s="2" t="n">
+      <c r="AB170" s="2" t="n">
         <v>12069.17</v>
       </c>
-      <c r="AA170" s="2" t="n">
+      <c r="AC170" s="2" t="n">
         <v>81477.61</v>
       </c>
-      <c r="AB170" s="2" t="n">
+      <c r="AD170" s="2" t="n">
         <v>20519.73</v>
       </c>
-      <c r="AC170" s="2" t="n">
+      <c r="AE170" s="2" t="n">
         <v>1312.96</v>
       </c>
     </row>
@@ -29457,33 +30483,39 @@
         <v>47882.2</v>
       </c>
       <c r="T171" s="3" t="n">
+        <v>43054.26185168209</v>
+      </c>
+      <c r="U171" s="3" t="n">
+        <v>4827.938476428795</v>
+      </c>
+      <c r="V171" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="U171" s="3" t="n">
+      <c r="W171" s="3" t="n">
         <v>3308.55</v>
       </c>
-      <c r="V171" s="3" t="n">
+      <c r="X171" s="3" t="n">
         <v>-5354.199467264814</v>
       </c>
-      <c r="W171" s="3" t="n">
+      <c r="Y171" s="3" t="n">
         <v>39655.29790656704</v>
       </c>
-      <c r="X171" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y171" s="3" t="n">
+      <c r="Z171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA171" s="3" t="n">
         <v>1063140.71</v>
       </c>
-      <c r="Z171" s="3" t="n">
+      <c r="AB171" s="3" t="n">
         <v>40844.58</v>
       </c>
-      <c r="AA171" s="3" t="n">
+      <c r="AC171" s="3" t="n">
         <v>67170.84</v>
       </c>
-      <c r="AB171" s="3" t="n">
+      <c r="AD171" s="3" t="n">
         <v>24332.81</v>
       </c>
-      <c r="AC171" s="3" t="n">
+      <c r="AE171" s="3" t="n">
         <v>1306.54</v>
       </c>
     </row>
@@ -29563,28 +30595,34 @@
         <v>0</v>
       </c>
       <c r="U172" s="2" t="n">
+        <v>83.82174170602877</v>
+      </c>
+      <c r="V172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W172" s="2" t="n">
         <v>1269.56</v>
       </c>
-      <c r="V172" s="2" t="inlineStr"/>
-      <c r="W172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X172" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X172" s="2" t="inlineStr"/>
       <c r="Y172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="2" t="n">
         <v>1072187.08</v>
       </c>
-      <c r="Z172" s="2" t="n">
+      <c r="AB172" s="2" t="n">
         <v>8095.11</v>
       </c>
-      <c r="AA172" s="2" t="n">
+      <c r="AC172" s="2" t="n">
         <v>86648.07000000001</v>
       </c>
-      <c r="AB172" s="2" t="n">
+      <c r="AD172" s="2" t="n">
         <v>20162.9</v>
       </c>
-      <c r="AC172" s="2" t="n">
+      <c r="AE172" s="2" t="n">
         <v>1312.52</v>
       </c>
     </row>
@@ -29661,33 +30699,39 @@
         <v>48626.74</v>
       </c>
       <c r="T173" s="3" t="n">
+        <v>43712.25322739236</v>
+      </c>
+      <c r="U173" s="3" t="n">
+        <v>4914.488305270137</v>
+      </c>
+      <c r="V173" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="U173" s="3" t="n">
+      <c r="W173" s="3" t="n">
         <v>2654.74</v>
       </c>
-      <c r="V173" s="3" t="n">
+      <c r="X173" s="3" t="n">
         <v>-1480.313096201513</v>
       </c>
-      <c r="W173" s="3" t="n">
+      <c r="Y173" s="3" t="n">
         <v>40712.25322739236</v>
       </c>
-      <c r="X173" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y173" s="3" t="n">
+      <c r="Z173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA173" s="3" t="n">
         <v>1066543.31</v>
       </c>
-      <c r="Z173" s="3" t="n">
+      <c r="AB173" s="3" t="n">
         <v>67659.39</v>
       </c>
-      <c r="AA173" s="3" t="n">
+      <c r="AC173" s="3" t="n">
         <v>74484.92</v>
       </c>
-      <c r="AB173" s="3" t="n">
+      <c r="AD173" s="3" t="n">
         <v>24429.85</v>
       </c>
-      <c r="AC173" s="3" t="n">
+      <c r="AE173" s="3" t="n">
         <v>1310.74</v>
       </c>
     </row>
@@ -29765,28 +30809,34 @@
         <v>0</v>
       </c>
       <c r="U174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W174" s="2" t="n">
         <v>1212.38</v>
       </c>
-      <c r="V174" s="2" t="inlineStr"/>
-      <c r="W174" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X174" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X174" s="2" t="inlineStr"/>
       <c r="Y174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA174" s="2" t="n">
         <v>1068619.5</v>
       </c>
-      <c r="Z174" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA174" s="2" t="n">
+      <c r="AB174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC174" s="2" t="n">
         <v>88803.42999999999</v>
       </c>
-      <c r="AB174" s="2" t="n">
+      <c r="AD174" s="2" t="n">
         <v>17760.69</v>
       </c>
-      <c r="AC174" s="2" t="n">
+      <c r="AE174" s="2" t="n">
         <v>1305.28</v>
       </c>
     </row>
@@ -29861,33 +30911,39 @@
         <v>43405.97</v>
       </c>
       <c r="T175" s="3" t="n">
+        <v>43405.97260902772</v>
+      </c>
+      <c r="U175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V175" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="U175" s="3" t="n">
+      <c r="W175" s="3" t="n">
         <v>2099.35</v>
       </c>
-      <c r="V175" s="3" t="n">
+      <c r="X175" s="3" t="n">
         <v>-1142.402054012287</v>
       </c>
-      <c r="W175" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X175" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA175" s="3" t="n">
         <v>1066670.74</v>
       </c>
-      <c r="Z175" s="3" t="n">
+      <c r="AB175" s="3" t="n">
         <v>251.06</v>
       </c>
-      <c r="AA175" s="3" t="n">
+      <c r="AC175" s="3" t="n">
         <v>130602.07</v>
       </c>
-      <c r="AB175" s="3" t="n">
+      <c r="AD175" s="3" t="n">
         <v>18568.48</v>
       </c>
-      <c r="AC175" s="3" t="n">
+      <c r="AE175" s="3" t="n">
         <v>1303.85</v>
       </c>
     </row>
@@ -29965,28 +31021,34 @@
         <v>0</v>
       </c>
       <c r="U176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W176" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V176" s="2" t="inlineStr"/>
-      <c r="W176" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X176" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X176" s="2" t="inlineStr"/>
       <c r="Y176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA176" s="2" t="n">
         <v>1068699.1</v>
       </c>
-      <c r="Z176" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA176" s="2" t="n">
+      <c r="AB176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC176" s="2" t="n">
         <v>89003.78</v>
       </c>
-      <c r="AB176" s="2" t="n">
+      <c r="AD176" s="2" t="n">
         <v>17800.76</v>
       </c>
-      <c r="AC176" s="2" t="n">
+      <c r="AE176" s="2" t="n">
         <v>1305.37</v>
       </c>
     </row>
@@ -30061,33 +31123,39 @@
         <v>43712.25</v>
       </c>
       <c r="T177" s="3" t="n">
+        <v>43712.25322739236</v>
+      </c>
+      <c r="U177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V177" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="U177" s="3" t="n">
+      <c r="W177" s="3" t="n">
         <v>2092.18</v>
       </c>
-      <c r="V177" s="3" t="n">
+      <c r="X177" s="3" t="n">
         <v>-1214.132802264299</v>
       </c>
-      <c r="W177" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X177" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA177" s="3" t="n">
         <v>1066710.52</v>
       </c>
-      <c r="Z177" s="3" t="n">
+      <c r="AB177" s="3" t="n">
         <v>251.06</v>
       </c>
-      <c r="AA177" s="3" t="n">
+      <c r="AC177" s="3" t="n">
         <v>131094.45</v>
       </c>
-      <c r="AB177" s="3" t="n">
+      <c r="AD177" s="3" t="n">
         <v>18576.65</v>
       </c>
-      <c r="AC177" s="3" t="n">
+      <c r="AE177" s="3" t="n">
         <v>1303.91</v>
       </c>
     </row>
@@ -30165,28 +31233,34 @@
         <v>0</v>
       </c>
       <c r="U178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W178" s="2" t="n">
         <v>1501.27</v>
       </c>
-      <c r="V178" s="2" t="inlineStr"/>
-      <c r="W178" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X178" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X178" s="2" t="inlineStr"/>
       <c r="Y178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA178" s="2" t="n">
         <v>1157232.26</v>
       </c>
-      <c r="Z178" s="2" t="n">
+      <c r="AB178" s="2" t="n">
         <v>-1490.64</v>
       </c>
-      <c r="AA178" s="2" t="n">
+      <c r="AC178" s="2" t="n">
         <v>151574.05</v>
       </c>
-      <c r="AB178" s="2" t="n">
+      <c r="AD178" s="2" t="n">
         <v>30016.68</v>
       </c>
-      <c r="AC178" s="2" t="n">
+      <c r="AE178" s="2" t="n">
         <v>1438.46</v>
       </c>
     </row>
@@ -30261,33 +31335,39 @@
         <v>7380.82</v>
       </c>
       <c r="T179" s="3" t="n">
+        <v>7380.822416302763</v>
+      </c>
+      <c r="U179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V179" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U179" s="3" t="n">
+      <c r="W179" s="3" t="n">
         <v>1652.75</v>
       </c>
-      <c r="V179" s="3" t="n">
+      <c r="X179" s="3" t="n">
         <v>-656.6091416769195</v>
       </c>
-      <c r="W179" s="3" t="n">
+      <c r="Y179" s="3" t="n">
         <v>4380.822416302763</v>
       </c>
-      <c r="X179" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y179" s="3" t="n">
+      <c r="Z179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="3" t="n">
         <v>1156287.46</v>
       </c>
-      <c r="Z179" s="3" t="n">
+      <c r="AB179" s="3" t="n">
         <v>-1512.86</v>
       </c>
-      <c r="AA179" s="3" t="n">
+      <c r="AC179" s="3" t="n">
         <v>157403.07</v>
       </c>
-      <c r="AB179" s="3" t="n">
+      <c r="AD179" s="3" t="n">
         <v>31178.04</v>
       </c>
-      <c r="AC179" s="3" t="n">
+      <c r="AE179" s="3" t="n">
         <v>1437.67</v>
       </c>
     </row>
@@ -30365,28 +31445,34 @@
         <v>0</v>
       </c>
       <c r="U180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W180" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V180" s="2" t="inlineStr"/>
-      <c r="W180" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X180" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X180" s="2" t="inlineStr"/>
       <c r="Y180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA180" s="2" t="n">
         <v>1157653.05</v>
       </c>
-      <c r="Z180" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA180" s="2" t="n">
+      <c r="AB180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC180" s="2" t="n">
         <v>200363.27</v>
       </c>
-      <c r="AB180" s="2" t="n">
+      <c r="AD180" s="2" t="n">
         <v>40072.65</v>
       </c>
-      <c r="AC180" s="2" t="n">
+      <c r="AE180" s="2" t="n">
         <v>1439</v>
       </c>
     </row>
@@ -30461,33 +31547,39 @@
         <v>7380.82</v>
       </c>
       <c r="T181" s="3" t="n">
+        <v>7380.822416302763</v>
+      </c>
+      <c r="U181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V181" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U181" s="3" t="n">
+      <c r="W181" s="3" t="n">
         <v>1348.67</v>
       </c>
-      <c r="V181" s="3" t="n">
+      <c r="X181" s="3" t="n">
         <v>-633.7767853625119</v>
       </c>
-      <c r="W181" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X181" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="3" t="n">
         <v>1156278.03</v>
       </c>
-      <c r="Z181" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA181" s="3" t="n">
+      <c r="AB181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC181" s="3" t="n">
         <v>206210.42</v>
       </c>
-      <c r="AB181" s="3" t="n">
+      <c r="AD181" s="3" t="n">
         <v>40815.92</v>
       </c>
-      <c r="AC181" s="3" t="n">
+      <c r="AE181" s="3" t="n">
         <v>1436.98</v>
       </c>
     </row>
@@ -30565,28 +31657,34 @@
         <v>0</v>
       </c>
       <c r="U182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W182" s="2" t="n">
         <v>1198.56</v>
       </c>
-      <c r="V182" s="2" t="inlineStr"/>
-      <c r="W182" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X182" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X182" s="2" t="inlineStr"/>
       <c r="Y182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA182" s="2" t="n">
         <v>1157653.05</v>
       </c>
-      <c r="Z182" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA182" s="2" t="n">
+      <c r="AB182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC182" s="2" t="n">
         <v>200363.27</v>
       </c>
-      <c r="AB182" s="2" t="n">
+      <c r="AD182" s="2" t="n">
         <v>40072.65</v>
       </c>
-      <c r="AC182" s="2" t="n">
+      <c r="AE182" s="2" t="n">
         <v>1439</v>
       </c>
     </row>
@@ -30661,33 +31759,39 @@
         <v>7380.82</v>
       </c>
       <c r="T183" s="3" t="n">
+        <v>7380.822416302763</v>
+      </c>
+      <c r="U183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V183" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U183" s="3" t="n">
+      <c r="W183" s="3" t="n">
         <v>1348.67</v>
       </c>
-      <c r="V183" s="3" t="n">
+      <c r="X183" s="3" t="n">
         <v>-633.7767853625119</v>
       </c>
-      <c r="W183" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X183" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA183" s="3" t="n">
         <v>1156278.03</v>
       </c>
-      <c r="Z183" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA183" s="3" t="n">
+      <c r="AB183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC183" s="3" t="n">
         <v>206210.42</v>
       </c>
-      <c r="AB183" s="3" t="n">
+      <c r="AD183" s="3" t="n">
         <v>40815.92</v>
       </c>
-      <c r="AC183" s="3" t="n">
+      <c r="AE183" s="3" t="n">
         <v>1436.98</v>
       </c>
     </row>
@@ -30767,28 +31871,34 @@
         <v>0</v>
       </c>
       <c r="U184" s="2" t="n">
+        <v>1134.257247698002</v>
+      </c>
+      <c r="V184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W184" s="2" t="n">
         <v>1691.33</v>
       </c>
-      <c r="V184" s="2" t="inlineStr"/>
-      <c r="W184" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X184" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X184" s="2" t="inlineStr"/>
       <c r="Y184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA184" s="2" t="n">
         <v>1135635.06</v>
       </c>
-      <c r="Z184" s="2" t="n">
+      <c r="AB184" s="2" t="n">
         <v>1251.66</v>
       </c>
-      <c r="AA184" s="2" t="n">
+      <c r="AC184" s="2" t="n">
         <v>137375.01</v>
       </c>
-      <c r="AB184" s="2" t="n">
+      <c r="AD184" s="2" t="n">
         <v>27913.08</v>
       </c>
-      <c r="AC184" s="2" t="n">
+      <c r="AE184" s="2" t="n">
         <v>1405.07</v>
       </c>
     </row>
@@ -30865,33 +31975,39 @@
         <v>10351.06</v>
       </c>
       <c r="T185" s="3" t="n">
+        <v>9527.419443046414</v>
+      </c>
+      <c r="U185" s="3" t="n">
+        <v>823.6420724221042</v>
+      </c>
+      <c r="V185" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="U185" s="3" t="n">
+      <c r="W185" s="3" t="n">
         <v>1870.65</v>
       </c>
-      <c r="V185" s="3" t="n">
+      <c r="X185" s="3" t="n">
         <v>1873.706186780706</v>
       </c>
-      <c r="W185" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X185" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA185" s="3" t="n">
         <v>1135778.55</v>
       </c>
-      <c r="Z185" s="3" t="n">
+      <c r="AB185" s="3" t="n">
         <v>1150.7</v>
       </c>
-      <c r="AA185" s="3" t="n">
+      <c r="AC185" s="3" t="n">
         <v>144637.89</v>
       </c>
-      <c r="AB185" s="3" t="n">
+      <c r="AD185" s="3" t="n">
         <v>29330.32</v>
       </c>
-      <c r="AC185" s="3" t="n">
+      <c r="AE185" s="3" t="n">
         <v>1407.31</v>
       </c>
     </row>
@@ -30971,28 +32087,34 @@
         <v>0</v>
       </c>
       <c r="U186" s="2" t="n">
+        <v>238.041792858316</v>
+      </c>
+      <c r="V186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W186" s="2" t="n">
         <v>1478.51</v>
       </c>
-      <c r="V186" s="2" t="inlineStr"/>
-      <c r="W186" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X186" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X186" s="2" t="inlineStr"/>
       <c r="Y186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA186" s="2" t="n">
         <v>1137483.51</v>
       </c>
-      <c r="Z186" s="2" t="n">
+      <c r="AB186" s="2" t="n">
         <v>219.92</v>
       </c>
-      <c r="AA186" s="2" t="n">
+      <c r="AC186" s="2" t="n">
         <v>152839.85</v>
       </c>
-      <c r="AB186" s="2" t="n">
+      <c r="AD186" s="2" t="n">
         <v>30644.94</v>
       </c>
-      <c r="AC186" s="2" t="n">
+      <c r="AE186" s="2" t="n">
         <v>1407.98</v>
       </c>
     </row>
@@ -31069,33 +32191,39 @@
         <v>8064.65</v>
       </c>
       <c r="T187" s="3" t="n">
+        <v>7905.793914210568</v>
+      </c>
+      <c r="U187" s="3" t="n">
+        <v>158.8576024653326</v>
+      </c>
+      <c r="V187" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="U187" s="3" t="n">
+      <c r="W187" s="3" t="n">
         <v>1644.21</v>
       </c>
-      <c r="V187" s="3" t="n">
+      <c r="X187" s="3" t="n">
         <v>1252.726471790113</v>
       </c>
-      <c r="W187" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X187" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="3" t="n">
         <v>1137390.23</v>
       </c>
-      <c r="Z187" s="3" t="n">
+      <c r="AB187" s="3" t="n">
         <v>223.94</v>
       </c>
-      <c r="AA187" s="3" t="n">
+      <c r="AC187" s="3" t="n">
         <v>158794.54</v>
       </c>
-      <c r="AB187" s="3" t="n">
+      <c r="AD187" s="3" t="n">
         <v>31837.29</v>
       </c>
-      <c r="AC187" s="3" t="n">
+      <c r="AE187" s="3" t="n">
         <v>1409.48</v>
       </c>
     </row>
@@ -31175,28 +32303,34 @@
         <v>0</v>
       </c>
       <c r="U188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W188" s="2" t="n">
         <v>1323.63</v>
       </c>
-      <c r="V188" s="2" t="inlineStr"/>
-      <c r="W188" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X188" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X188" s="2" t="inlineStr"/>
       <c r="Y188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA188" s="2" t="n">
         <v>1143888.39</v>
       </c>
-      <c r="Z188" s="2" t="n">
+      <c r="AB188" s="2" t="n">
         <v>-1365.08</v>
       </c>
-      <c r="AA188" s="2" t="n">
+      <c r="AC188" s="2" t="n">
         <v>174905.42</v>
       </c>
-      <c r="AB188" s="2" t="n">
+      <c r="AD188" s="2" t="n">
         <v>34503.31</v>
       </c>
-      <c r="AC188" s="2" t="n">
+      <c r="AE188" s="2" t="n">
         <v>1420.68</v>
       </c>
     </row>
@@ -31273,33 +32407,39 @@
         <v>7380.82</v>
       </c>
       <c r="T189" s="3" t="n">
+        <v>7380.822416302763</v>
+      </c>
+      <c r="U189" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V189" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U189" s="3" t="n">
+      <c r="W189" s="3" t="n">
         <v>1472.97</v>
       </c>
-      <c r="V189" s="3" t="n">
+      <c r="X189" s="3" t="n">
         <v>-429.1075967266224</v>
       </c>
-      <c r="W189" s="3" t="n">
+      <c r="Y189" s="3" t="n">
         <v>4380.822416302763</v>
       </c>
-      <c r="X189" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y189" s="3" t="n">
+      <c r="Z189" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="3" t="n">
         <v>1143799.51</v>
       </c>
-      <c r="Z189" s="3" t="n">
+      <c r="AB189" s="3" t="n">
         <v>-1323.31</v>
       </c>
-      <c r="AA189" s="3" t="n">
+      <c r="AC189" s="3" t="n">
         <v>181067.42</v>
       </c>
-      <c r="AB189" s="3" t="n">
+      <c r="AD189" s="3" t="n">
         <v>35750.33</v>
       </c>
-      <c r="AC189" s="3" t="n">
+      <c r="AE189" s="3" t="n">
         <v>1420.17</v>
       </c>
     </row>
@@ -31377,28 +32517,34 @@
         <v>0</v>
       </c>
       <c r="U190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W190" s="2" t="n">
         <v>1418.42</v>
       </c>
-      <c r="V190" s="2" t="inlineStr"/>
-      <c r="W190" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X190" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X190" s="2" t="inlineStr"/>
       <c r="Y190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="2" t="n">
         <v>1143145.58</v>
       </c>
-      <c r="Z190" s="2" t="n">
+      <c r="AB190" s="2" t="n">
         <v>238.25</v>
       </c>
-      <c r="AA190" s="2" t="n">
+      <c r="AC190" s="2" t="n">
         <v>159379.95</v>
       </c>
-      <c r="AB190" s="2" t="n">
+      <c r="AD190" s="2" t="n">
         <v>31959.38</v>
       </c>
-      <c r="AC190" s="2" t="n">
+      <c r="AE190" s="2" t="n">
         <v>1416.73</v>
       </c>
     </row>
@@ -31473,33 +32619,39 @@
         <v>7771.35</v>
       </c>
       <c r="T191" s="3" t="n">
+        <v>7771.349654831092</v>
+      </c>
+      <c r="U191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V191" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="U191" s="3" t="n">
+      <c r="W191" s="3" t="n">
         <v>1576.92</v>
       </c>
-      <c r="V191" s="3" t="n">
+      <c r="X191" s="3" t="n">
         <v>382.2613698455971</v>
       </c>
-      <c r="W191" s="3" t="n">
+      <c r="Y191" s="3" t="n">
         <v>1732.182695779806</v>
       </c>
-      <c r="X191" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y191" s="3" t="n">
+      <c r="Z191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA191" s="3" t="n">
         <v>1142669.87</v>
       </c>
-      <c r="Z191" s="3" t="n">
+      <c r="AB191" s="3" t="n">
         <v>233.65</v>
       </c>
-      <c r="AA191" s="3" t="n">
+      <c r="AC191" s="3" t="n">
         <v>165760.81</v>
       </c>
-      <c r="AB191" s="3" t="n">
+      <c r="AD191" s="3" t="n">
         <v>33198.89</v>
       </c>
-      <c r="AC191" s="3" t="n">
+      <c r="AE191" s="3" t="n">
         <v>1417.19</v>
       </c>
     </row>
@@ -31577,28 +32729,34 @@
         <v>0</v>
       </c>
       <c r="U192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W192" s="2" t="n">
         <v>1420.81</v>
       </c>
-      <c r="V192" s="2" t="inlineStr"/>
-      <c r="W192" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X192" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="X192" s="2" t="inlineStr"/>
       <c r="Y192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA192" s="2" t="n">
         <v>1149245.95</v>
       </c>
-      <c r="Z192" s="2" t="n">
+      <c r="AB192" s="2" t="n">
         <v>-222.49</v>
       </c>
-      <c r="AA192" s="2" t="n">
+      <c r="AC192" s="2" t="n">
         <v>161607.38</v>
       </c>
-      <c r="AB192" s="2" t="n">
+      <c r="AD192" s="2" t="n">
         <v>32276.98</v>
       </c>
-      <c r="AC192" s="2" t="n">
+      <c r="AE192" s="2" t="n">
         <v>1426.43</v>
       </c>
     </row>
@@ -31673,33 +32831,39 @@
         <v>7380.82</v>
       </c>
       <c r="T193" s="3" t="n">
+        <v>7380.822416302763</v>
+      </c>
+      <c r="U193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V193" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U193" s="3" t="n">
+      <c r="W193" s="3" t="n">
         <v>1571.52</v>
       </c>
-      <c r="V193" s="3" t="n">
+      <c r="X193" s="3" t="n">
         <v>-628.1973052928224</v>
       </c>
-      <c r="W193" s="3" t="n">
+      <c r="Y193" s="3" t="n">
         <v>4380.822416302763</v>
       </c>
-      <c r="X193" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y193" s="3" t="n">
+      <c r="Z193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA193" s="3" t="n">
         <v>1148324</v>
       </c>
-      <c r="Z193" s="3" t="n">
+      <c r="AB193" s="3" t="n">
         <v>-234.1</v>
       </c>
-      <c r="AA193" s="3" t="n">
+      <c r="AC193" s="3" t="n">
         <v>167543.92</v>
       </c>
-      <c r="AB193" s="3" t="n">
+      <c r="AD193" s="3" t="n">
         <v>33461.96</v>
       </c>
-      <c r="AC193" s="3" t="n">
+      <c r="AE193" s="3" t="n">
         <v>1425.68</v>
       </c>
     </row>
